--- a/Content/Data/WeaponData.xlsx
+++ b/Content/Data/WeaponData.xlsx
@@ -8,14 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeaponTypes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rarity" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Localization" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pistol" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AssaultRifle" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SniperRifle" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SubMachineGun" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShotGun" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Localization" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pistol" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AssaultRifle" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SniperRifle" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SubMachineGun" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShotGun" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -236,12 +235,90 @@
     <author>Weapon Data Schema</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>이 시트의 TypeID는 각 무기 타입 시트 이름과 반드시 일치해야 합니다.
-(예: 'Pistol' 시트가 있으면 여기에도 TypeID='Pistol' 행이 있어야 함)
-새로운 무기 카테고리(Sword, Bow, Spear 등)를 추가할 때도
-이 시트에 행을 먼저 추가한 뒤, 같은 이름의 시트를 만들면 됩니다.</t>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>등급 값 (Common/Rare/Epic). 실제 정의(DropWeight/SellValue 등)는 RandomBox.xlsx의 Rarity 시트가 유일한 출처.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>실제 텍스트가 아니라 Localization 시트를 참조하는 키.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>실제 텍스트가 아니라 Localization 시트를 참조하는 키.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>발당(펠릿당) 데미지. 총 데미지 = Damage x PelletCount.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>한 번 발사에 판정되는 펠릿 수. 일반 무기는 1, ShotGun만 1보다 큼.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>초당 발사 횟수(RPS). FireInterval = 1 / FireRate_RPS
+FireMode=Burst인 경우: 버스트와 버스트 사이 재사격 간격을 의미.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>발사 방식: Single / Burst / FullAuto</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>FireMode=Burst일 때만 의미 있는 값. 그 외에는 0.</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Burst 내부 발사 간격(초). FireRate_RPS(버스트간 간격)와 별개. 그 외에는 0.</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0">
+      <text>
+        <t>TRUE=히트스캔, FALSE=투사체.</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0">
+      <text>
+        <t>조준(ADS) 가능 여부. FALSE면 이 무기는 조준 자체가 불가능.</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
+      <text>
+        <t>조준경/가늠자 배율. 조준경 없으면 1.0.</t>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0" shapeId="0">
+      <text>
+        <t>무조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
+      </text>
+    </comment>
+    <comment ref="AA1" authorId="0" shapeId="0">
+      <text>
+        <t>조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
+      </text>
+    </comment>
+    <comment ref="AD1" authorId="0" shapeId="0">
+      <text>
+        <t>예약 필드 (현재 미사용). 추후 카메라 반동 전환 시 사용 예정.</t>
+      </text>
+    </comment>
+    <comment ref="AE1" authorId="0" shapeId="0">
+      <text>
+        <t>예약 필드 (현재 미사용). RecoilVertical과 동일 목적.</t>
+      </text>
+    </comment>
+    <comment ref="AG1" authorId="0" shapeId="0">
+      <text>
+        <t>조준(ADS) 중 이동속도 배율. MoveSpeedMultiplier와 별개로 조준 시 추가 적용.</t>
       </text>
     </comment>
   </commentList>
@@ -254,12 +331,90 @@
     <author>Weapon Data Schema</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>이 시트의 RarityID는 Weapon 시트의 Rarity 컬럼 값과 반드시 일치해야 합니다.
-DropWeight: 랜덤 무기상자/맵 스폰에서 이 등급이 뽑힐 상대 가중치.
-SellValue: 이 등급 무기를 판매할 때 지급되는 고정 크레딧 값
-(무기 개별 판매가는 없고, 등급의 SellValue를 그대로 사용).</t>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>등급 값 (Common/Rare/Epic). 실제 정의(DropWeight/SellValue 등)는 RandomBox.xlsx의 Rarity 시트가 유일한 출처.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>실제 텍스트가 아니라 Localization 시트를 참조하는 키.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>실제 텍스트가 아니라 Localization 시트를 참조하는 키.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>발당(펠릿당) 데미지. 총 데미지 = Damage x PelletCount.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>한 번 발사에 판정되는 펠릿 수. 일반 무기는 1, ShotGun만 1보다 큼.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>초당 발사 횟수(RPS). FireInterval = 1 / FireRate_RPS
+FireMode=Burst인 경우: 버스트와 버스트 사이 재사격 간격을 의미.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>발사 방식: Single / Burst / FullAuto</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>FireMode=Burst일 때만 의미 있는 값. 그 외에는 0.</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Burst 내부 발사 간격(초). FireRate_RPS(버스트간 간격)와 별개. 그 외에는 0.</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0">
+      <text>
+        <t>TRUE=히트스캔, FALSE=투사체.</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0">
+      <text>
+        <t>조준(ADS) 가능 여부. FALSE면 이 무기는 조준 자체가 불가능.</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
+      <text>
+        <t>조준경/가늠자 배율. 조준경 없으면 1.0.</t>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0" shapeId="0">
+      <text>
+        <t>무조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
+      </text>
+    </comment>
+    <comment ref="AA1" authorId="0" shapeId="0">
+      <text>
+        <t>조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
+      </text>
+    </comment>
+    <comment ref="AD1" authorId="0" shapeId="0">
+      <text>
+        <t>예약 필드 (현재 미사용). 추후 카메라 반동 전환 시 사용 예정.</t>
+      </text>
+    </comment>
+    <comment ref="AE1" authorId="0" shapeId="0">
+      <text>
+        <t>예약 필드 (현재 미사용). RecoilVertical과 동일 목적.</t>
+      </text>
+    </comment>
+    <comment ref="AG1" authorId="0" shapeId="0">
+      <text>
+        <t>조준(ADS) 중 이동속도 배율. MoveSpeedMultiplier와 별개로 조준 시 추가 적용.</t>
       </text>
     </comment>
   </commentList>
@@ -272,11 +427,90 @@
     <author>Weapon Data Schema</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>Weapon 시트의 NameKey/DescKey가 참조하는 키.
-언어를 추가하려면 오른쪽에 컬럼(예: ja, zh-Hans)만 추가하면 됨.
-모든 언어 컬럼에 빈 칸이 없어야 컨버터 검증을 통과함.</t>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>등급 값 (Common/Rare/Epic). 실제 정의(DropWeight/SellValue 등)는 RandomBox.xlsx의 Rarity 시트가 유일한 출처.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>실제 텍스트가 아니라 Localization 시트를 참조하는 키.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>실제 텍스트가 아니라 Localization 시트를 참조하는 키.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>발당(펠릿당) 데미지. 총 데미지 = Damage x PelletCount.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>한 번 발사에 판정되는 펠릿 수. 일반 무기는 1, ShotGun만 1보다 큼.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>초당 발사 횟수(RPS). FireInterval = 1 / FireRate_RPS
+FireMode=Burst인 경우: 버스트와 버스트 사이 재사격 간격을 의미.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>발사 방식: Single / Burst / FullAuto</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>FireMode=Burst일 때만 의미 있는 값. 그 외에는 0.</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Burst 내부 발사 간격(초). FireRate_RPS(버스트간 간격)와 별개. 그 외에는 0.</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0">
+      <text>
+        <t>TRUE=히트스캔, FALSE=투사체.</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0">
+      <text>
+        <t>조준(ADS) 가능 여부. FALSE면 이 무기는 조준 자체가 불가능.</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
+      <text>
+        <t>조준경/가늠자 배율. 조준경 없으면 1.0.</t>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0" shapeId="0">
+      <text>
+        <t>무조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
+      </text>
+    </comment>
+    <comment ref="AA1" authorId="0" shapeId="0">
+      <text>
+        <t>조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
+      </text>
+    </comment>
+    <comment ref="AD1" authorId="0" shapeId="0">
+      <text>
+        <t>예약 필드 (현재 미사용). 추후 카메라 반동 전환 시 사용 예정.</t>
+      </text>
+    </comment>
+    <comment ref="AE1" authorId="0" shapeId="0">
+      <text>
+        <t>예약 필드 (현재 미사용). RecoilVertical과 동일 목적.</t>
+      </text>
+    </comment>
+    <comment ref="AG1" authorId="0" shapeId="0">
+      <text>
+        <t>조준(ADS) 중 이동속도 배율. MoveSpeedMultiplier와 별개로 조준 시 추가 적용.</t>
       </text>
     </comment>
   </commentList>
@@ -289,99 +523,90 @@
     <author>Weapon Data Schema</author>
   </authors>
   <commentList>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>등급 값 (Common/Rare/Epic). 실제 정의(DropWeight/SellValue 등)는 RandomBox.xlsx의 Rarity 시트가 유일한 출처.</t>
+      </text>
+    </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>실제 텍스트가 아니라 Localization 시트를 참조하는 키.
-형식: {Index}.Name (예: P_1.Name)
-Localization 시트에 이 키와 각 언어 컬럼 값이 있어야 함.</t>
+        <t>실제 텍스트가 아니라 Localization 시트를 참조하는 키.</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>실제 텍스트가 아니라 Localization 시트를 참조하는 키.
-형식: {Index}.Description (예: P_1.Description)</t>
+        <t>실제 텍스트가 아니라 Localization 시트를 참조하는 키.</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>발당(펠릿당) 데미지. 실제 총 데미지 = Damage x PelletCount.
-일반 무기는 PelletCount=1이라 사실상 Damage가 곧 총 데미지.</t>
+        <t>발당(펠릿당) 데미지. 총 데미지 = Damage x PelletCount.</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>한 번 발사에 판정되는 펠릿(투사체) 수.
-일반 무기는 1로 고정, ShotGun처럼 산탄이 여러 개인 무기만 1보다 큼.</t>
+        <t>한 번 발사에 판정되는 펠릿 수. 일반 무기는 1, ShotGun만 1보다 큼.</t>
       </text>
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
-        <t>초당 발사 횟수(RPS) 기준.
-언리얼 발사 간격 계산: FireInterval = 1 / FireRate_RPS
-예: SR_1 = 0.67 (약 1.5초에 1발, 볼트액션)
-FireMode=Burst인 경우: '버스트와 버스트 사이' 재사격 간격을 의미함
-(버스트 내부 발사 간격은 BurstShotInterval 사용).</t>
+        <t>초당 발사 횟수(RPS). FireInterval = 1 / FireRate_RPS
+FireMode=Burst인 경우: 버스트와 버스트 사이 재사격 간격을 의미.</t>
       </text>
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>발사 방식. 값: Single / Burst / FullAuto</t>
+        <t>발사 방식: Single / Burst / FullAuto</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>FireMode=Burst일 때만 의미 있는 값. 그 외 FireMode에서는 0.</t>
+        <t>FireMode=Burst일 때만 의미 있는 값. 그 외에는 0.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
       <text>
-        <t>FireMode=Burst일 때, 버스트 '내부'에서 한 발과 다음 발 사이의 간격(초).
-FireRate_RPS(버스트간 간격)와는 별개 값. 그 외 FireMode에서는 0.</t>
+        <t>Burst 내부 발사 간격(초). FireRate_RPS(버스트간 간격)와 별개. 그 외에는 0.</t>
       </text>
     </comment>
     <comment ref="S1" authorId="0" shapeId="0">
       <text>
-        <t>TRUE = 히트스캔 판정, FALSE = 투사체(Projectile) 판정.
-FALSE인 경우 ProjectileSpeed 값이 반드시 필요.</t>
+        <t>TRUE=히트스캔, FALSE=투사체.</t>
       </text>
     </comment>
     <comment ref="U1" authorId="0" shapeId="0">
       <text>
-        <t>조준(ADS) 가능 여부. FALSE면 이 무기는 조준 자체가 불가능 (예: 추후 추가될 일부 근접무기).</t>
+        <t>조준(ADS) 가능 여부. FALSE면 이 무기는 조준 자체가 불가능.</t>
       </text>
     </comment>
     <comment ref="V1" authorId="0" shapeId="0">
       <text>
-        <t>조준경/가늠자 배율. 조준경이 없는 무기는 1.0(배율 없음)으로 설정.
-예: SR_1 = 6.0 (6배율 스코프), 일반 소총 = 1.0~2.0 (기계식/도트/저배율).</t>
+        <t>조준경/가늠자 배율. 조준경 없으면 1.0.</t>
       </text>
     </comment>
     <comment ref="Z1" authorId="0" shapeId="0">
       <text>
-        <t>무조준(Hipfire) 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
+        <t>무조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
       </text>
     </comment>
     <comment ref="AA1" authorId="0" shapeId="0">
       <text>
-        <t>조준(ADS) 상태에서 탄퍼짐이 도달할 수 있는 최대치 (보통 Hipfire보다 작음).</t>
+        <t>조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
       </text>
     </comment>
     <comment ref="AD1" authorId="0" shapeId="0">
       <text>
-        <t>예약 필드 (현재 미사용)
-현재는 탄퍼짐(bloom) 기반 반동만 사용 중.
-추후 카메라/에임 이동형 반동으로 밸런싱 전환 시 사용 예정.
-지금은 0으로 두거나 공란으로 둘 것.</t>
+        <t>예약 필드 (현재 미사용). 추후 카메라 반동 전환 시 사용 예정.</t>
       </text>
     </comment>
     <comment ref="AE1" authorId="0" shapeId="0">
       <text>
-        <t>예약 필드 (현재 미사용) - RecoilVertical과 동일한 목적.</t>
+        <t>예약 필드 (현재 미사용). RecoilVertical과 동일 목적.</t>
       </text>
     </comment>
     <comment ref="AG1" authorId="0" shapeId="0">
       <text>
-        <t>조준(ADS) 중 이동속도 배율. MoveSpeedMultiplier(장착 중 기본 이동속도)와는 별개로, 조준 시 추가로 적용됨.</t>
+        <t>조준(ADS) 중 이동속도 배율. MoveSpeedMultiplier와 별개로 조준 시 추가 적용.</t>
       </text>
     </comment>
   </commentList>
@@ -394,414 +619,90 @@
     <author>Weapon Data Schema</author>
   </authors>
   <commentList>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>등급 값 (Common/Rare/Epic). 실제 정의(DropWeight/SellValue 등)는 RandomBox.xlsx의 Rarity 시트가 유일한 출처.</t>
+      </text>
+    </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>실제 텍스트가 아니라 Localization 시트를 참조하는 키.
-형식: {Index}.Name (예: P_1.Name)
-Localization 시트에 이 키와 각 언어 컬럼 값이 있어야 함.</t>
+        <t>실제 텍스트가 아니라 Localization 시트를 참조하는 키.</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>실제 텍스트가 아니라 Localization 시트를 참조하는 키.
-형식: {Index}.Description (예: P_1.Description)</t>
+        <t>실제 텍스트가 아니라 Localization 시트를 참조하는 키.</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>발당(펠릿당) 데미지. 실제 총 데미지 = Damage x PelletCount.
-일반 무기는 PelletCount=1이라 사실상 Damage가 곧 총 데미지.</t>
+        <t>발당(펠릿당) 데미지. 총 데미지 = Damage x PelletCount.</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>한 번 발사에 판정되는 펠릿(투사체) 수.
-일반 무기는 1로 고정, ShotGun처럼 산탄이 여러 개인 무기만 1보다 큼.</t>
+        <t>한 번 발사에 판정되는 펠릿 수. 일반 무기는 1, ShotGun만 1보다 큼.</t>
       </text>
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
-        <t>초당 발사 횟수(RPS) 기준.
-언리얼 발사 간격 계산: FireInterval = 1 / FireRate_RPS
-예: SR_1 = 0.67 (약 1.5초에 1발, 볼트액션)
-FireMode=Burst인 경우: '버스트와 버스트 사이' 재사격 간격을 의미함
-(버스트 내부 발사 간격은 BurstShotInterval 사용).</t>
+        <t>초당 발사 횟수(RPS). FireInterval = 1 / FireRate_RPS
+FireMode=Burst인 경우: 버스트와 버스트 사이 재사격 간격을 의미.</t>
       </text>
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>발사 방식. 값: Single / Burst / FullAuto</t>
+        <t>발사 방식: Single / Burst / FullAuto</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>FireMode=Burst일 때만 의미 있는 값. 그 외 FireMode에서는 0.</t>
+        <t>FireMode=Burst일 때만 의미 있는 값. 그 외에는 0.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
       <text>
-        <t>FireMode=Burst일 때, 버스트 '내부'에서 한 발과 다음 발 사이의 간격(초).
-FireRate_RPS(버스트간 간격)와는 별개 값. 그 외 FireMode에서는 0.</t>
+        <t>Burst 내부 발사 간격(초). FireRate_RPS(버스트간 간격)와 별개. 그 외에는 0.</t>
       </text>
     </comment>
     <comment ref="S1" authorId="0" shapeId="0">
       <text>
-        <t>TRUE = 히트스캔 판정, FALSE = 투사체(Projectile) 판정.
-FALSE인 경우 ProjectileSpeed 값이 반드시 필요.</t>
+        <t>TRUE=히트스캔, FALSE=투사체.</t>
       </text>
     </comment>
     <comment ref="U1" authorId="0" shapeId="0">
       <text>
-        <t>조준(ADS) 가능 여부. FALSE면 이 무기는 조준 자체가 불가능 (예: 추후 추가될 일부 근접무기).</t>
+        <t>조준(ADS) 가능 여부. FALSE면 이 무기는 조준 자체가 불가능.</t>
       </text>
     </comment>
     <comment ref="V1" authorId="0" shapeId="0">
       <text>
-        <t>조준경/가늠자 배율. 조준경이 없는 무기는 1.0(배율 없음)으로 설정.
-예: SR_1 = 6.0 (6배율 스코프), 일반 소총 = 1.0~2.0 (기계식/도트/저배율).</t>
+        <t>조준경/가늠자 배율. 조준경 없으면 1.0.</t>
       </text>
     </comment>
     <comment ref="Z1" authorId="0" shapeId="0">
       <text>
-        <t>무조준(Hipfire) 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
+        <t>무조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
       </text>
     </comment>
     <comment ref="AA1" authorId="0" shapeId="0">
       <text>
-        <t>조준(ADS) 상태에서 탄퍼짐이 도달할 수 있는 최대치 (보통 Hipfire보다 작음).</t>
+        <t>조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
       </text>
     </comment>
     <comment ref="AD1" authorId="0" shapeId="0">
       <text>
-        <t>예약 필드 (현재 미사용)
-현재는 탄퍼짐(bloom) 기반 반동만 사용 중.
-추후 카메라/에임 이동형 반동으로 밸런싱 전환 시 사용 예정.
-지금은 0으로 두거나 공란으로 둘 것.</t>
+        <t>예약 필드 (현재 미사용). 추후 카메라 반동 전환 시 사용 예정.</t>
       </text>
     </comment>
     <comment ref="AE1" authorId="0" shapeId="0">
       <text>
-        <t>예약 필드 (현재 미사용) - RecoilVertical과 동일한 목적.</t>
+        <t>예약 필드 (현재 미사용). RecoilVertical과 동일 목적.</t>
       </text>
     </comment>
     <comment ref="AG1" authorId="0" shapeId="0">
       <text>
-        <t>조준(ADS) 중 이동속도 배율. MoveSpeedMultiplier(장착 중 기본 이동속도)와는 별개로, 조준 시 추가로 적용됨.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Weapon Data Schema</author>
-  </authors>
-  <commentList>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>실제 텍스트가 아니라 Localization 시트를 참조하는 키.
-형식: {Index}.Name (예: P_1.Name)
-Localization 시트에 이 키와 각 언어 컬럼 값이 있어야 함.</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>실제 텍스트가 아니라 Localization 시트를 참조하는 키.
-형식: {Index}.Description (예: P_1.Description)</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>발당(펠릿당) 데미지. 실제 총 데미지 = Damage x PelletCount.
-일반 무기는 PelletCount=1이라 사실상 Damage가 곧 총 데미지.</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>한 번 발사에 판정되는 펠릿(투사체) 수.
-일반 무기는 1로 고정, ShotGun처럼 산탄이 여러 개인 무기만 1보다 큼.</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>초당 발사 횟수(RPS) 기준.
-언리얼 발사 간격 계산: FireInterval = 1 / FireRate_RPS
-예: SR_1 = 0.67 (약 1.5초에 1발, 볼트액션)
-FireMode=Burst인 경우: '버스트와 버스트 사이' 재사격 간격을 의미함
-(버스트 내부 발사 간격은 BurstShotInterval 사용).</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>발사 방식. 값: Single / Burst / FullAuto</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t>FireMode=Burst일 때만 의미 있는 값. 그 외 FireMode에서는 0.</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t>FireMode=Burst일 때, 버스트 '내부'에서 한 발과 다음 발 사이의 간격(초).
-FireRate_RPS(버스트간 간격)와는 별개 값. 그 외 FireMode에서는 0.</t>
-      </text>
-    </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
-      <text>
-        <t>TRUE = 히트스캔 판정, FALSE = 투사체(Projectile) 판정.
-FALSE인 경우 ProjectileSpeed 값이 반드시 필요.</t>
-      </text>
-    </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
-      <text>
-        <t>조준(ADS) 가능 여부. FALSE면 이 무기는 조준 자체가 불가능 (예: 추후 추가될 일부 근접무기).</t>
-      </text>
-    </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
-      <text>
-        <t>조준경/가늠자 배율. 조준경이 없는 무기는 1.0(배율 없음)으로 설정.
-예: SR_1 = 6.0 (6배율 스코프), 일반 소총 = 1.0~2.0 (기계식/도트/저배율).</t>
-      </text>
-    </comment>
-    <comment ref="Z1" authorId="0" shapeId="0">
-      <text>
-        <t>무조준(Hipfire) 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
-      </text>
-    </comment>
-    <comment ref="AA1" authorId="0" shapeId="0">
-      <text>
-        <t>조준(ADS) 상태에서 탄퍼짐이 도달할 수 있는 최대치 (보통 Hipfire보다 작음).</t>
-      </text>
-    </comment>
-    <comment ref="AD1" authorId="0" shapeId="0">
-      <text>
-        <t>예약 필드 (현재 미사용)
-현재는 탄퍼짐(bloom) 기반 반동만 사용 중.
-추후 카메라/에임 이동형 반동으로 밸런싱 전환 시 사용 예정.
-지금은 0으로 두거나 공란으로 둘 것.</t>
-      </text>
-    </comment>
-    <comment ref="AE1" authorId="0" shapeId="0">
-      <text>
-        <t>예약 필드 (현재 미사용) - RecoilVertical과 동일한 목적.</t>
-      </text>
-    </comment>
-    <comment ref="AG1" authorId="0" shapeId="0">
-      <text>
-        <t>조준(ADS) 중 이동속도 배율. MoveSpeedMultiplier(장착 중 기본 이동속도)와는 별개로, 조준 시 추가로 적용됨.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Weapon Data Schema</author>
-  </authors>
-  <commentList>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>실제 텍스트가 아니라 Localization 시트를 참조하는 키.
-형식: {Index}.Name (예: P_1.Name)
-Localization 시트에 이 키와 각 언어 컬럼 값이 있어야 함.</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>실제 텍스트가 아니라 Localization 시트를 참조하는 키.
-형식: {Index}.Description (예: P_1.Description)</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>발당(펠릿당) 데미지. 실제 총 데미지 = Damage x PelletCount.
-일반 무기는 PelletCount=1이라 사실상 Damage가 곧 총 데미지.</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>한 번 발사에 판정되는 펠릿(투사체) 수.
-일반 무기는 1로 고정, ShotGun처럼 산탄이 여러 개인 무기만 1보다 큼.</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>초당 발사 횟수(RPS) 기준.
-언리얼 발사 간격 계산: FireInterval = 1 / FireRate_RPS
-예: SR_1 = 0.67 (약 1.5초에 1발, 볼트액션)
-FireMode=Burst인 경우: '버스트와 버스트 사이' 재사격 간격을 의미함
-(버스트 내부 발사 간격은 BurstShotInterval 사용).</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>발사 방식. 값: Single / Burst / FullAuto</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t>FireMode=Burst일 때만 의미 있는 값. 그 외 FireMode에서는 0.</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t>FireMode=Burst일 때, 버스트 '내부'에서 한 발과 다음 발 사이의 간격(초).
-FireRate_RPS(버스트간 간격)와는 별개 값. 그 외 FireMode에서는 0.</t>
-      </text>
-    </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
-      <text>
-        <t>TRUE = 히트스캔 판정, FALSE = 투사체(Projectile) 판정.
-FALSE인 경우 ProjectileSpeed 값이 반드시 필요.</t>
-      </text>
-    </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
-      <text>
-        <t>조준(ADS) 가능 여부. FALSE면 이 무기는 조준 자체가 불가능 (예: 추후 추가될 일부 근접무기).</t>
-      </text>
-    </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
-      <text>
-        <t>조준경/가늠자 배율. 조준경이 없는 무기는 1.0(배율 없음)으로 설정.
-예: SR_1 = 6.0 (6배율 스코프), 일반 소총 = 1.0~2.0 (기계식/도트/저배율).</t>
-      </text>
-    </comment>
-    <comment ref="Z1" authorId="0" shapeId="0">
-      <text>
-        <t>무조준(Hipfire) 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
-      </text>
-    </comment>
-    <comment ref="AA1" authorId="0" shapeId="0">
-      <text>
-        <t>조준(ADS) 상태에서 탄퍼짐이 도달할 수 있는 최대치 (보통 Hipfire보다 작음).</t>
-      </text>
-    </comment>
-    <comment ref="AD1" authorId="0" shapeId="0">
-      <text>
-        <t>예약 필드 (현재 미사용)
-현재는 탄퍼짐(bloom) 기반 반동만 사용 중.
-추후 카메라/에임 이동형 반동으로 밸런싱 전환 시 사용 예정.
-지금은 0으로 두거나 공란으로 둘 것.</t>
-      </text>
-    </comment>
-    <comment ref="AE1" authorId="0" shapeId="0">
-      <text>
-        <t>예약 필드 (현재 미사용) - RecoilVertical과 동일한 목적.</t>
-      </text>
-    </comment>
-    <comment ref="AG1" authorId="0" shapeId="0">
-      <text>
-        <t>조준(ADS) 중 이동속도 배율. MoveSpeedMultiplier(장착 중 기본 이동속도)와는 별개로, 조준 시 추가로 적용됨.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment8.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Weapon Data Schema</author>
-  </authors>
-  <commentList>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>실제 텍스트가 아니라 Localization 시트를 참조하는 키.
-형식: {Index}.Name (예: P_1.Name)
-Localization 시트에 이 키와 각 언어 컬럼 값이 있어야 함.</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>실제 텍스트가 아니라 Localization 시트를 참조하는 키.
-형식: {Index}.Description (예: P_1.Description)</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>발당(펠릿당) 데미지. 실제 총 데미지 = Damage x PelletCount.
-일반 무기는 PelletCount=1이라 사실상 Damage가 곧 총 데미지.</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>한 번 발사에 판정되는 펠릿(투사체) 수.
-일반 무기는 1로 고정, ShotGun처럼 산탄이 여러 개인 무기만 1보다 큼.</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>초당 발사 횟수(RPS) 기준.
-언리얼 발사 간격 계산: FireInterval = 1 / FireRate_RPS
-예: SR_1 = 0.67 (약 1.5초에 1발, 볼트액션)
-FireMode=Burst인 경우: '버스트와 버스트 사이' 재사격 간격을 의미함
-(버스트 내부 발사 간격은 BurstShotInterval 사용).</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>발사 방식. 값: Single / Burst / FullAuto</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t>FireMode=Burst일 때만 의미 있는 값. 그 외 FireMode에서는 0.</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t>FireMode=Burst일 때, 버스트 '내부'에서 한 발과 다음 발 사이의 간격(초).
-FireRate_RPS(버스트간 간격)와는 별개 값. 그 외 FireMode에서는 0.</t>
-      </text>
-    </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
-      <text>
-        <t>TRUE = 히트스캔 판정, FALSE = 투사체(Projectile) 판정.
-FALSE인 경우 ProjectileSpeed 값이 반드시 필요.</t>
-      </text>
-    </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
-      <text>
-        <t>조준(ADS) 가능 여부. FALSE면 이 무기는 조준 자체가 불가능 (예: 추후 추가될 일부 근접무기).</t>
-      </text>
-    </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
-      <text>
-        <t>조준경/가늠자 배율. 조준경이 없는 무기는 1.0(배율 없음)으로 설정.
-예: SR_1 = 6.0 (6배율 스코프), 일반 소총 = 1.0~2.0 (기계식/도트/저배율).</t>
-      </text>
-    </comment>
-    <comment ref="Z1" authorId="0" shapeId="0">
-      <text>
-        <t>무조준(Hipfire) 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
-      </text>
-    </comment>
-    <comment ref="AA1" authorId="0" shapeId="0">
-      <text>
-        <t>조준(ADS) 상태에서 탄퍼짐이 도달할 수 있는 최대치 (보통 Hipfire보다 작음).</t>
-      </text>
-    </comment>
-    <comment ref="AD1" authorId="0" shapeId="0">
-      <text>
-        <t>예약 필드 (현재 미사용)
-현재는 탄퍼짐(bloom) 기반 반동만 사용 중.
-추후 카메라/에임 이동형 반동으로 밸런싱 전환 시 사용 예정.
-지금은 0으로 두거나 공란으로 둘 것.</t>
-      </text>
-    </comment>
-    <comment ref="AE1" authorId="0" shapeId="0">
-      <text>
-        <t>예약 필드 (현재 미사용) - RecoilVertical과 동일한 목적.</t>
-      </text>
-    </comment>
-    <comment ref="AG1" authorId="0" shapeId="0">
-      <text>
-        <t>조준(ADS) 중 이동속도 배율. MoveSpeedMultiplier(장착 중 기본 이동속도)와는 별개로, 조준 시 추가로 적용됨.</t>
+        <t>조준(ADS) 중 이동속도 배율. MoveSpeedMultiplier와 별개로 조준 시 추가 적용.</t>
       </text>
     </comment>
   </commentList>
@@ -1108,7 +1009,7 @@
     <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TypeID</t>
@@ -1135,7 +1036,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="14" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1299,157 +1200,10 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00FFC000"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="13.2" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>RarityID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>DisplayName</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Color</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>DropWeight</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>SellValue</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>#B0B0B0</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>희귀</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>#3B82F6</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>영웅</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>#A855F7</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>800</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0000B0F0"/>
@@ -1464,7 +1218,7 @@
     <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Key</t>
@@ -1608,12 +1362,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>장거리에서 원샷킬을 노릴 수 있는 볼트액션 저격소총.</t>
+          <t>장거리에서 원샷킬을 노릴 수 있는 저격소총.</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>A bolt-action sniper rifle capable of long-range one-shot kills.</t>
+          <t>A sniper rifle capable of long-range one-shot kills.</t>
         </is>
       </c>
     </row>
@@ -1687,11 +1441,10 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008EA9DB"/>
@@ -2216,11 +1969,8 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation sqref="S3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="U3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="S3 U3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -2238,7 +1988,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0070AD47"/>
@@ -2886,11 +2636,8 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation sqref="S3:S4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="U3:U4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="S3:S4 U3:U4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation sqref="B3:B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -2908,7 +2655,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -3433,11 +3180,8 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation sqref="S3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="U3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="S3 U3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -3455,7 +3199,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BF8F00"/>
@@ -3980,11 +3724,8 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation sqref="S3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="U3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="S3 U3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -4002,7 +3743,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>
@@ -4541,11 +4282,8 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation sqref="S3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="U3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="S3 U3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -4563,7 +4301,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4575,7 +4313,7 @@
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4618,7 +4356,7 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>고유 인덱스. 예: P_1, AR_1, AR_2, SR_1, SMG_1, SG_1. 절대 변경 금지.</t>
+          <t>고유 인덱스. 절대 변경 금지.</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4378,7 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>해당 시트에 고정된 타입 값 (Pistol/AssaultRifle/SniperRifle/SubMachineGun/ShotGun).</t>
+          <t>해당 시트에 고정된 타입 값.</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4400,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Rarity 마스터 시트 참조 (Common/Rare/Epic). 판매가는 Rarity.SellValue 사용, Weapon엔 별도 CreditValue 없음.</t>
+          <t>등급 값 (Common/Rare/Epic). 실제 정의는 RandomBox.xlsx의 Rarity 시트.</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4422,7 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>인게임 표시 이름의 로컬라이징 키. 실제 문자열은 Localization 시트에서 관리.</t>
+          <t>로컬라이징 키 (표시 이름).</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4444,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>UI 설명 텍스트의 로컬라이징 키. 실제 문자열은 Localization 시트에서 관리.</t>
+          <t>로컬라이징 키 (설명).</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4488,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>한 번 발사에 판정되는 펠릿 수. 일반 무기는 1, ShotGun만 1보다 큼.</t>
+          <t>한 번 발사에 판정되는 펠릿 수.</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4532,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>초당 발사 횟수(RPS). FireInterval = 1 / FireRate_RPS. Burst에서는 버스트간 간격.</t>
+          <t>초당 발사 횟수(RPS). Burst에서는 버스트간 간격.</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4576,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>FireMode=Burst일 때만 의미 있는 값. 그 외 FireMode에서는 0.</t>
+          <t>FireMode=Burst일 때만 의미 있는 값.</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4598,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Burst 내부 발사 간격(초). FireRate_RPS(버스트간 간격)와 별개. 그 외에는 0.</t>
+          <t>Burst 내부 발사 간격(초).</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4686,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>데미지 감소가 시작되는 거리.</t>
+          <t>데미지 감소 시작 거리.</t>
         </is>
       </c>
     </row>
@@ -4992,7 +4730,7 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>MaxRange 도달 시 최소 데미지.</t>
+          <t>최소 데미지.</t>
         </is>
       </c>
     </row>
@@ -5036,7 +4774,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>투사체 속도. Hitscan이면 0.</t>
+          <t>투사체 속도.</t>
         </is>
       </c>
     </row>
@@ -5058,7 +4796,7 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>조준(ADS) 가능 여부. FALSE면 이 무기는 조준 자체가 불가능.</t>
+          <t>조준(ADS) 가능 여부.</t>
         </is>
       </c>
     </row>
@@ -5080,7 +4818,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>조준경/가늠자 배율. 조준경 없으면 1.0.</t>
+          <t>조준경 배율. 없으면 1.0.</t>
         </is>
       </c>
     </row>
@@ -5102,7 +4840,7 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>무조준 상태 탄착 분산도(기본값).</t>
+          <t>무조준 탄착 분산도.</t>
         </is>
       </c>
     </row>
@@ -5124,7 +4862,7 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>조준(ADS) 상태 탄착 분산도(기본값).</t>
+          <t>조준 탄착 분산도.</t>
         </is>
       </c>
     </row>
@@ -5168,7 +4906,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>무조준 상태에서 탄퍼짐 최대 한계치.</t>
+          <t>무조준 탄퍼짐 최대치.</t>
         </is>
       </c>
     </row>
@@ -5190,7 +4928,7 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>조준 상태에서 탄퍼짐 최대 한계치 (보통 Hipfire보다 작음).</t>
+          <t>조준 탄퍼짐 최대치.</t>
         </is>
       </c>
     </row>
@@ -5212,7 +4950,7 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>사격 정지 후 탄퍼짐 회복 시작까지 딜레이(초).</t>
+          <t>탄퍼짐 회복 시작 딜레이(초).</t>
         </is>
       </c>
     </row>
@@ -5256,7 +4994,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>현재 미사용. 추후 카메라 반동 도입 시 사용 예정 필드.</t>
+          <t>미사용.</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5016,7 @@
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>현재 미사용. 추후 카메라 반동 도입 시 사용 예정 필드.</t>
+          <t>미사용.</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5038,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>조준(ADS) 전환 소요 시간(초).</t>
+          <t>조준 전환 소요 시간(초).</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5060,7 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>조준(ADS) 중 이동속도 배율.</t>
+          <t>조준 중 이동속도 배율.</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5082,7 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>무기 장착 중 기본 이동속도 배율.</t>
+          <t>장착 중 기본 이동속도 배율.</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5104,7 @@
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>무기 교체(꺼내기) 소요 시간(초).</t>
+          <t>무기 교체 소요 시간(초).</t>
         </is>
       </c>
     </row>

--- a/Content/Data/WeaponData.xlsx
+++ b/Content/Data/WeaponData.xlsx
@@ -281,42 +281,60 @@
         <t>Burst 내부 발사 간격(초). FireRate_RPS(버스트간 간격)와 별개. 그 외에는 0.</t>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>장전 가능 여부. FALSE면 이 무기는 장전 자체가 불가능(탄창 교체 없음).</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>장전 시 필요한 마나(기본 요구치). 프로토타입 기준 MagazineSize와 동일하게 설정.
+실제 소비량 = WeaponReqMana - (MaxAmmo - CurAmmo) x ManaPerAmmo
+(MaxAmmo=MagazineSize, CurAmmo는 런타임 상태값이라 데이터에 없음)
+CanReload=FALSE인 무기도 값은 유지 - 추후 장전 가능으로 바뀔 수 있음.</t>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <t>탄 1발당 요구 마나 감소분. CanReload=FALSE인 무기도 값은 유지(추후 변경 대비).</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
       <text>
         <t>TRUE=히트스캔, FALSE=투사체.</t>
       </text>
     </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
+    <comment ref="X1" authorId="0" shapeId="0">
       <text>
         <t>조준(ADS) 가능 여부. FALSE면 이 무기는 조준 자체가 불가능.</t>
       </text>
     </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
+    <comment ref="Y1" authorId="0" shapeId="0">
       <text>
         <t>조준경/가늠자 배율. 조준경 없으면 1.0.</t>
       </text>
     </comment>
-    <comment ref="Z1" authorId="0" shapeId="0">
+    <comment ref="AC1" authorId="0" shapeId="0">
       <text>
         <t>무조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
       </text>
     </comment>
-    <comment ref="AA1" authorId="0" shapeId="0">
+    <comment ref="AD1" authorId="0" shapeId="0">
       <text>
         <t>조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
       </text>
     </comment>
-    <comment ref="AD1" authorId="0" shapeId="0">
+    <comment ref="AG1" authorId="0" shapeId="0">
       <text>
         <t>예약 필드 (현재 미사용). 추후 카메라 반동 전환 시 사용 예정.</t>
       </text>
     </comment>
-    <comment ref="AE1" authorId="0" shapeId="0">
+    <comment ref="AH1" authorId="0" shapeId="0">
       <text>
         <t>예약 필드 (현재 미사용). RecoilVertical과 동일 목적.</t>
       </text>
     </comment>
-    <comment ref="AG1" authorId="0" shapeId="0">
+    <comment ref="AJ1" authorId="0" shapeId="0">
       <text>
         <t>조준(ADS) 중 이동속도 배율. MoveSpeedMultiplier와 별개로 조준 시 추가 적용.</t>
       </text>
@@ -377,42 +395,60 @@
         <t>Burst 내부 발사 간격(초). FireRate_RPS(버스트간 간격)와 별개. 그 외에는 0.</t>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>장전 가능 여부. FALSE면 이 무기는 장전 자체가 불가능(탄창 교체 없음).</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>장전 시 필요한 마나(기본 요구치). 프로토타입 기준 MagazineSize와 동일하게 설정.
+실제 소비량 = WeaponReqMana - (MaxAmmo - CurAmmo) x ManaPerAmmo
+(MaxAmmo=MagazineSize, CurAmmo는 런타임 상태값이라 데이터에 없음)
+CanReload=FALSE인 무기도 값은 유지 - 추후 장전 가능으로 바뀔 수 있음.</t>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <t>탄 1발당 요구 마나 감소분. CanReload=FALSE인 무기도 값은 유지(추후 변경 대비).</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
       <text>
         <t>TRUE=히트스캔, FALSE=투사체.</t>
       </text>
     </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
+    <comment ref="X1" authorId="0" shapeId="0">
       <text>
         <t>조준(ADS) 가능 여부. FALSE면 이 무기는 조준 자체가 불가능.</t>
       </text>
     </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
+    <comment ref="Y1" authorId="0" shapeId="0">
       <text>
         <t>조준경/가늠자 배율. 조준경 없으면 1.0.</t>
       </text>
     </comment>
-    <comment ref="Z1" authorId="0" shapeId="0">
+    <comment ref="AC1" authorId="0" shapeId="0">
       <text>
         <t>무조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
       </text>
     </comment>
-    <comment ref="AA1" authorId="0" shapeId="0">
+    <comment ref="AD1" authorId="0" shapeId="0">
       <text>
         <t>조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
       </text>
     </comment>
-    <comment ref="AD1" authorId="0" shapeId="0">
+    <comment ref="AG1" authorId="0" shapeId="0">
       <text>
         <t>예약 필드 (현재 미사용). 추후 카메라 반동 전환 시 사용 예정.</t>
       </text>
     </comment>
-    <comment ref="AE1" authorId="0" shapeId="0">
+    <comment ref="AH1" authorId="0" shapeId="0">
       <text>
         <t>예약 필드 (현재 미사용). RecoilVertical과 동일 목적.</t>
       </text>
     </comment>
-    <comment ref="AG1" authorId="0" shapeId="0">
+    <comment ref="AJ1" authorId="0" shapeId="0">
       <text>
         <t>조준(ADS) 중 이동속도 배율. MoveSpeedMultiplier와 별개로 조준 시 추가 적용.</t>
       </text>
@@ -473,42 +509,60 @@
         <t>Burst 내부 발사 간격(초). FireRate_RPS(버스트간 간격)와 별개. 그 외에는 0.</t>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>장전 가능 여부. FALSE면 이 무기는 장전 자체가 불가능(탄창 교체 없음).</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>장전 시 필요한 마나(기본 요구치). 프로토타입 기준 MagazineSize와 동일하게 설정.
+실제 소비량 = WeaponReqMana - (MaxAmmo - CurAmmo) x ManaPerAmmo
+(MaxAmmo=MagazineSize, CurAmmo는 런타임 상태값이라 데이터에 없음)
+CanReload=FALSE인 무기도 값은 유지 - 추후 장전 가능으로 바뀔 수 있음.</t>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <t>탄 1발당 요구 마나 감소분. CanReload=FALSE인 무기도 값은 유지(추후 변경 대비).</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
       <text>
         <t>TRUE=히트스캔, FALSE=투사체.</t>
       </text>
     </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
+    <comment ref="X1" authorId="0" shapeId="0">
       <text>
         <t>조준(ADS) 가능 여부. FALSE면 이 무기는 조준 자체가 불가능.</t>
       </text>
     </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
+    <comment ref="Y1" authorId="0" shapeId="0">
       <text>
         <t>조준경/가늠자 배율. 조준경 없으면 1.0.</t>
       </text>
     </comment>
-    <comment ref="Z1" authorId="0" shapeId="0">
+    <comment ref="AC1" authorId="0" shapeId="0">
       <text>
         <t>무조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
       </text>
     </comment>
-    <comment ref="AA1" authorId="0" shapeId="0">
+    <comment ref="AD1" authorId="0" shapeId="0">
       <text>
         <t>조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
       </text>
     </comment>
-    <comment ref="AD1" authorId="0" shapeId="0">
+    <comment ref="AG1" authorId="0" shapeId="0">
       <text>
         <t>예약 필드 (현재 미사용). 추후 카메라 반동 전환 시 사용 예정.</t>
       </text>
     </comment>
-    <comment ref="AE1" authorId="0" shapeId="0">
+    <comment ref="AH1" authorId="0" shapeId="0">
       <text>
         <t>예약 필드 (현재 미사용). RecoilVertical과 동일 목적.</t>
       </text>
     </comment>
-    <comment ref="AG1" authorId="0" shapeId="0">
+    <comment ref="AJ1" authorId="0" shapeId="0">
       <text>
         <t>조준(ADS) 중 이동속도 배율. MoveSpeedMultiplier와 별개로 조준 시 추가 적용.</t>
       </text>
@@ -569,42 +623,60 @@
         <t>Burst 내부 발사 간격(초). FireRate_RPS(버스트간 간격)와 별개. 그 외에는 0.</t>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>장전 가능 여부. FALSE면 이 무기는 장전 자체가 불가능(탄창 교체 없음).</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>장전 시 필요한 마나(기본 요구치). 프로토타입 기준 MagazineSize와 동일하게 설정.
+실제 소비량 = WeaponReqMana - (MaxAmmo - CurAmmo) x ManaPerAmmo
+(MaxAmmo=MagazineSize, CurAmmo는 런타임 상태값이라 데이터에 없음)
+CanReload=FALSE인 무기도 값은 유지 - 추후 장전 가능으로 바뀔 수 있음.</t>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <t>탄 1발당 요구 마나 감소분. CanReload=FALSE인 무기도 값은 유지(추후 변경 대비).</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
       <text>
         <t>TRUE=히트스캔, FALSE=투사체.</t>
       </text>
     </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
+    <comment ref="X1" authorId="0" shapeId="0">
       <text>
         <t>조준(ADS) 가능 여부. FALSE면 이 무기는 조준 자체가 불가능.</t>
       </text>
     </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
+    <comment ref="Y1" authorId="0" shapeId="0">
       <text>
         <t>조준경/가늠자 배율. 조준경 없으면 1.0.</t>
       </text>
     </comment>
-    <comment ref="Z1" authorId="0" shapeId="0">
+    <comment ref="AC1" authorId="0" shapeId="0">
       <text>
         <t>무조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
       </text>
     </comment>
-    <comment ref="AA1" authorId="0" shapeId="0">
+    <comment ref="AD1" authorId="0" shapeId="0">
       <text>
         <t>조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
       </text>
     </comment>
-    <comment ref="AD1" authorId="0" shapeId="0">
+    <comment ref="AG1" authorId="0" shapeId="0">
       <text>
         <t>예약 필드 (현재 미사용). 추후 카메라 반동 전환 시 사용 예정.</t>
       </text>
     </comment>
-    <comment ref="AE1" authorId="0" shapeId="0">
+    <comment ref="AH1" authorId="0" shapeId="0">
       <text>
         <t>예약 필드 (현재 미사용). RecoilVertical과 동일 목적.</t>
       </text>
     </comment>
-    <comment ref="AG1" authorId="0" shapeId="0">
+    <comment ref="AJ1" authorId="0" shapeId="0">
       <text>
         <t>조준(ADS) 중 이동속도 배율. MoveSpeedMultiplier와 별개로 조준 시 추가 적용.</t>
       </text>
@@ -665,42 +737,60 @@
         <t>Burst 내부 발사 간격(초). FireRate_RPS(버스트간 간격)와 별개. 그 외에는 0.</t>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>장전 가능 여부. FALSE면 이 무기는 장전 자체가 불가능(탄창 교체 없음).</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>장전 시 필요한 마나(기본 요구치). 프로토타입 기준 MagazineSize와 동일하게 설정.
+실제 소비량 = WeaponReqMana - (MaxAmmo - CurAmmo) x ManaPerAmmo
+(MaxAmmo=MagazineSize, CurAmmo는 런타임 상태값이라 데이터에 없음)
+CanReload=FALSE인 무기도 값은 유지 - 추후 장전 가능으로 바뀔 수 있음.</t>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <t>탄 1발당 요구 마나 감소분. CanReload=FALSE인 무기도 값은 유지(추후 변경 대비).</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
       <text>
         <t>TRUE=히트스캔, FALSE=투사체.</t>
       </text>
     </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
+    <comment ref="X1" authorId="0" shapeId="0">
       <text>
         <t>조준(ADS) 가능 여부. FALSE면 이 무기는 조준 자체가 불가능.</t>
       </text>
     </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
+    <comment ref="Y1" authorId="0" shapeId="0">
       <text>
         <t>조준경/가늠자 배율. 조준경 없으면 1.0.</t>
       </text>
     </comment>
-    <comment ref="Z1" authorId="0" shapeId="0">
+    <comment ref="AC1" authorId="0" shapeId="0">
       <text>
         <t>무조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
       </text>
     </comment>
-    <comment ref="AA1" authorId="0" shapeId="0">
+    <comment ref="AD1" authorId="0" shapeId="0">
       <text>
         <t>조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
       </text>
     </comment>
-    <comment ref="AD1" authorId="0" shapeId="0">
+    <comment ref="AG1" authorId="0" shapeId="0">
       <text>
         <t>예약 필드 (현재 미사용). 추후 카메라 반동 전환 시 사용 예정.</t>
       </text>
     </comment>
-    <comment ref="AE1" authorId="0" shapeId="0">
+    <comment ref="AH1" authorId="0" shapeId="0">
       <text>
         <t>예약 필드 (현재 미사용). RecoilVertical과 동일 목적.</t>
       </text>
     </comment>
-    <comment ref="AG1" authorId="0" shapeId="0">
+    <comment ref="AJ1" authorId="0" shapeId="0">
       <text>
         <t>조준(ADS) 중 이동속도 배율. MoveSpeedMultiplier와 별개로 조준 시 추가 적용.</t>
       </text>
@@ -1451,7 +1541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI3"/>
+  <dimension ref="A1:AL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1469,26 +1559,29 @@
     <col width="13.2" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="19.8" customWidth="1" min="16" max="16"/>
-    <col width="17.6" customWidth="1" min="17" max="17"/>
-    <col width="17.6" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="16.5" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="15.4" customWidth="1" min="22" max="22"/>
-    <col width="14.3" customWidth="1" min="23" max="23"/>
+    <col width="14.3" customWidth="1" min="16" max="16"/>
+    <col width="12.1" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="19.8" customWidth="1" min="19" max="19"/>
+    <col width="17.6" customWidth="1" min="20" max="20"/>
+    <col width="17.6" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="16.5" customWidth="1" min="23" max="23"/>
     <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="23.1" customWidth="1" min="25" max="25"/>
-    <col width="23.1" customWidth="1" min="26" max="26"/>
-    <col width="18.7" customWidth="1" min="27" max="27"/>
-    <col width="20.9" customWidth="1" min="28" max="28"/>
-    <col width="19.8" customWidth="1" min="29" max="29"/>
-    <col width="15.4" customWidth="1" min="30" max="30"/>
-    <col width="17.6" customWidth="1" min="31" max="31"/>
-    <col width="10" customWidth="1" min="32" max="32"/>
-    <col width="24.2" customWidth="1" min="33" max="33"/>
-    <col width="20.9" customWidth="1" min="34" max="34"/>
+    <col width="15.4" customWidth="1" min="25" max="25"/>
+    <col width="14.3" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="23.1" customWidth="1" min="28" max="28"/>
+    <col width="23.1" customWidth="1" min="29" max="29"/>
+    <col width="18.7" customWidth="1" min="30" max="30"/>
+    <col width="20.9" customWidth="1" min="31" max="31"/>
+    <col width="19.8" customWidth="1" min="32" max="32"/>
+    <col width="15.4" customWidth="1" min="33" max="33"/>
+    <col width="17.6" customWidth="1" min="34" max="34"/>
     <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="24.2" customWidth="1" min="36" max="36"/>
+    <col width="20.9" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -1564,105 +1657,120 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>CanReload</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>WeaponReqMana</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ManaPerAmmo</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>MaxRange</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>DamageFalloffStart</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>DamageFalloffEnd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>DamageFalloffMin</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>IsHitscan</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ProjectileSpeed</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>CanADS</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ScopeZoomLevel</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>SpreadHipfire</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>SpreadADS</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>SpreadIncreasePerShot</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MaxSpreadBloomHipfire</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MaxSpreadBloomADS</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>SpreadRecoveryDelay</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>SpreadRecoveryRate</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>RecoilVertical</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>RecoilHorizontal</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>ADSSpeed</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>ADSMoveSpeedMultiplier</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>MoveSpeedMultiplier</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>EquipTime</t>
         </is>
@@ -1741,7 +1849,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -1761,34 +1869,34 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>float</t>
@@ -1840,6 +1948,21 @@
         </is>
       </c>
       <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AL2" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -1900,77 +2023,88 @@
       <c r="N3" s="4" t="n">
         <v>1.8</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="4" t="n">
         <v>3000</v>
       </c>
-      <c r="P3" s="4" t="n">
+      <c r="S3" s="4" t="n">
         <v>1500</v>
       </c>
-      <c r="Q3" s="4" t="n">
+      <c r="T3" s="4" t="n">
         <v>3000</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="S3" s="6" t="inlineStr">
+      <c r="V3" s="6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T3" s="4" t="n">
+      <c r="W3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U3" s="6" t="inlineStr">
+      <c r="X3" s="6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="V3" s="4" t="n">
+      <c r="Y3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W3" s="4" t="n">
+      <c r="Z3" s="4" t="n">
         <v>3.5</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Y3" s="4" t="n">
+      <c r="AB3" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="Z3" s="4" t="n">
+      <c r="AC3" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AB3" s="4" t="n">
+      <c r="AE3" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="AC3" s="4" t="n">
+      <c r="AF3" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="AD3" s="7" t="n">
+      <c r="AG3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AE3" s="7" t="n">
+      <c r="AH3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AF3" s="4" t="n">
+      <c r="AI3" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="AH3" s="4" t="n">
+      <c r="AK3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="AI3" s="4" t="n">
+      <c r="AL3" s="4" t="n">
         <v>0.4</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="S3 U3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="O3 V3 X3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -1995,7 +2129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AL4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2013,26 +2147,29 @@
     <col width="13.2" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="19.8" customWidth="1" min="16" max="16"/>
-    <col width="17.6" customWidth="1" min="17" max="17"/>
-    <col width="17.6" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="16.5" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="15.4" customWidth="1" min="22" max="22"/>
-    <col width="14.3" customWidth="1" min="23" max="23"/>
+    <col width="14.3" customWidth="1" min="16" max="16"/>
+    <col width="12.1" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="19.8" customWidth="1" min="19" max="19"/>
+    <col width="17.6" customWidth="1" min="20" max="20"/>
+    <col width="17.6" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="16.5" customWidth="1" min="23" max="23"/>
     <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="23.1" customWidth="1" min="25" max="25"/>
-    <col width="23.1" customWidth="1" min="26" max="26"/>
-    <col width="18.7" customWidth="1" min="27" max="27"/>
-    <col width="20.9" customWidth="1" min="28" max="28"/>
-    <col width="19.8" customWidth="1" min="29" max="29"/>
-    <col width="15.4" customWidth="1" min="30" max="30"/>
-    <col width="17.6" customWidth="1" min="31" max="31"/>
-    <col width="10" customWidth="1" min="32" max="32"/>
-    <col width="24.2" customWidth="1" min="33" max="33"/>
-    <col width="20.9" customWidth="1" min="34" max="34"/>
+    <col width="15.4" customWidth="1" min="25" max="25"/>
+    <col width="14.3" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="23.1" customWidth="1" min="28" max="28"/>
+    <col width="23.1" customWidth="1" min="29" max="29"/>
+    <col width="18.7" customWidth="1" min="30" max="30"/>
+    <col width="20.9" customWidth="1" min="31" max="31"/>
+    <col width="19.8" customWidth="1" min="32" max="32"/>
+    <col width="15.4" customWidth="1" min="33" max="33"/>
+    <col width="17.6" customWidth="1" min="34" max="34"/>
     <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="24.2" customWidth="1" min="36" max="36"/>
+    <col width="20.9" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -2108,105 +2245,120 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>CanReload</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>WeaponReqMana</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ManaPerAmmo</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>MaxRange</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>DamageFalloffStart</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>DamageFalloffEnd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>DamageFalloffMin</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>IsHitscan</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ProjectileSpeed</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>CanADS</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ScopeZoomLevel</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>SpreadHipfire</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>SpreadADS</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>SpreadIncreasePerShot</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MaxSpreadBloomHipfire</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MaxSpreadBloomADS</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>SpreadRecoveryDelay</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>SpreadRecoveryRate</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>RecoilVertical</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>RecoilHorizontal</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>ADSSpeed</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>ADSMoveSpeedMultiplier</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>MoveSpeedMultiplier</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>EquipTime</t>
         </is>
@@ -2285,7 +2437,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -2305,34 +2457,34 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>float</t>
@@ -2384,6 +2536,21 @@
         </is>
       </c>
       <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AL2" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -2444,71 +2611,82 @@
       <c r="N3" s="4" t="n">
         <v>2.3</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="4" t="n">
         <v>6000</v>
       </c>
-      <c r="P3" s="4" t="n">
+      <c r="S3" s="4" t="n">
         <v>3000</v>
       </c>
-      <c r="Q3" s="4" t="n">
+      <c r="T3" s="4" t="n">
         <v>6000</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="S3" s="6" t="inlineStr">
+      <c r="V3" s="6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T3" s="4" t="n">
+      <c r="W3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U3" s="6" t="inlineStr">
+      <c r="X3" s="6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="V3" s="4" t="n">
+      <c r="Y3" s="4" t="n">
         <v>1.5</v>
       </c>
-      <c r="W3" s="4" t="n">
+      <c r="Z3" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="Y3" s="4" t="n">
+      <c r="AB3" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z3" s="4" t="n">
+      <c r="AC3" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="AB3" s="4" t="n">
+      <c r="AE3" s="4" t="n">
         <v>0.15</v>
       </c>
-      <c r="AC3" s="4" t="n">
+      <c r="AF3" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AD3" s="7" t="n">
+      <c r="AG3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AE3" s="7" t="n">
+      <c r="AH3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AF3" s="4" t="n">
+      <c r="AI3" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="AH3" s="4" t="n">
+      <c r="AK3" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="AI3" s="4" t="n">
+      <c r="AL3" s="4" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -2567,77 +2745,88 @@
       <c r="N4" s="4" t="n">
         <v>2.1</v>
       </c>
-      <c r="O4" s="4" t="n">
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="4" t="n">
         <v>6500</v>
       </c>
-      <c r="P4" s="4" t="n">
+      <c r="S4" s="4" t="n">
         <v>3200</v>
       </c>
-      <c r="Q4" s="4" t="n">
+      <c r="T4" s="4" t="n">
         <v>6500</v>
       </c>
-      <c r="R4" s="4" t="n">
+      <c r="U4" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="S4" s="6" t="inlineStr">
+      <c r="V4" s="6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T4" s="4" t="n">
+      <c r="W4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U4" s="6" t="inlineStr">
+      <c r="X4" s="6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="V4" s="4" t="n">
+      <c r="Y4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W4" s="4" t="n">
+      <c r="Z4" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="X4" s="4" t="n">
+      <c r="AA4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Y4" s="4" t="n">
+      <c r="AB4" s="4" t="n">
         <v>0.6</v>
       </c>
-      <c r="Z4" s="4" t="n">
+      <c r="AC4" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="AA4" s="4" t="n">
+      <c r="AD4" s="4" t="n">
         <v>3.5</v>
       </c>
-      <c r="AB4" s="4" t="n">
+      <c r="AE4" s="4" t="n">
         <v>0.15</v>
       </c>
-      <c r="AC4" s="4" t="n">
+      <c r="AF4" s="4" t="n">
         <v>5.5</v>
       </c>
-      <c r="AD4" s="7" t="n">
+      <c r="AG4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AE4" s="7" t="n">
+      <c r="AH4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AF4" s="4" t="n">
+      <c r="AI4" s="4" t="n">
         <v>0.22</v>
       </c>
-      <c r="AG4" s="4" t="n">
+      <c r="AJ4" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="AH4" s="4" t="n">
+      <c r="AK4" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="AI4" s="4" t="n">
+      <c r="AL4" s="4" t="n">
         <v>0.55</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="S3:S4 U3:U4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="O3:O4 V3:V4 X3:X4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation sqref="B3:B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -2662,7 +2851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI3"/>
+  <dimension ref="A1:AL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2680,26 +2869,29 @@
     <col width="13.2" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="19.8" customWidth="1" min="16" max="16"/>
-    <col width="17.6" customWidth="1" min="17" max="17"/>
-    <col width="17.6" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="16.5" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="15.4" customWidth="1" min="22" max="22"/>
-    <col width="14.3" customWidth="1" min="23" max="23"/>
+    <col width="14.3" customWidth="1" min="16" max="16"/>
+    <col width="12.1" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="19.8" customWidth="1" min="19" max="19"/>
+    <col width="17.6" customWidth="1" min="20" max="20"/>
+    <col width="17.6" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="16.5" customWidth="1" min="23" max="23"/>
     <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="23.1" customWidth="1" min="25" max="25"/>
-    <col width="23.1" customWidth="1" min="26" max="26"/>
-    <col width="18.7" customWidth="1" min="27" max="27"/>
-    <col width="20.9" customWidth="1" min="28" max="28"/>
-    <col width="19.8" customWidth="1" min="29" max="29"/>
-    <col width="15.4" customWidth="1" min="30" max="30"/>
-    <col width="17.6" customWidth="1" min="31" max="31"/>
-    <col width="10" customWidth="1" min="32" max="32"/>
-    <col width="24.2" customWidth="1" min="33" max="33"/>
-    <col width="20.9" customWidth="1" min="34" max="34"/>
+    <col width="15.4" customWidth="1" min="25" max="25"/>
+    <col width="14.3" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="23.1" customWidth="1" min="28" max="28"/>
+    <col width="23.1" customWidth="1" min="29" max="29"/>
+    <col width="18.7" customWidth="1" min="30" max="30"/>
+    <col width="20.9" customWidth="1" min="31" max="31"/>
+    <col width="19.8" customWidth="1" min="32" max="32"/>
+    <col width="15.4" customWidth="1" min="33" max="33"/>
+    <col width="17.6" customWidth="1" min="34" max="34"/>
     <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="24.2" customWidth="1" min="36" max="36"/>
+    <col width="20.9" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -2775,105 +2967,120 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>CanReload</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>WeaponReqMana</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ManaPerAmmo</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>MaxRange</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>DamageFalloffStart</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>DamageFalloffEnd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>DamageFalloffMin</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>IsHitscan</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ProjectileSpeed</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>CanADS</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ScopeZoomLevel</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>SpreadHipfire</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>SpreadADS</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>SpreadIncreasePerShot</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MaxSpreadBloomHipfire</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MaxSpreadBloomADS</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>SpreadRecoveryDelay</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>SpreadRecoveryRate</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>RecoilVertical</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>RecoilHorizontal</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>ADSSpeed</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>ADSMoveSpeedMultiplier</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>MoveSpeedMultiplier</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>EquipTime</t>
         </is>
@@ -2952,7 +3159,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -2972,34 +3179,34 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>float</t>
@@ -3051,6 +3258,21 @@
         </is>
       </c>
       <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AL2" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -3111,77 +3333,88 @@
       <c r="N3" s="4" t="n">
         <v>3.2</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="4" t="n">
         <v>15000</v>
       </c>
-      <c r="P3" s="4" t="n">
+      <c r="S3" s="4" t="n">
         <v>8000</v>
       </c>
-      <c r="Q3" s="4" t="n">
+      <c r="T3" s="4" t="n">
         <v>15000</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="S3" s="6" t="inlineStr">
+      <c r="V3" s="6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T3" s="4" t="n">
+      <c r="W3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U3" s="6" t="inlineStr">
+      <c r="X3" s="6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="V3" s="4" t="n">
+      <c r="Y3" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="W3" s="4" t="n">
+      <c r="Z3" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="Y3" s="4" t="n">
+      <c r="AB3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Z3" s="4" t="n">
+      <c r="AC3" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="AB3" s="4" t="n">
+      <c r="AE3" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC3" s="4" t="n">
+      <c r="AF3" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD3" s="7" t="n">
+      <c r="AG3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AE3" s="7" t="n">
+      <c r="AH3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AF3" s="4" t="n">
+      <c r="AI3" s="4" t="n">
         <v>0.45</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="AH3" s="4" t="n">
+      <c r="AK3" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="AI3" s="4" t="n">
+      <c r="AL3" s="4" t="n">
         <v>0.8</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="S3 U3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="O3 V3 X3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -3206,7 +3439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI3"/>
+  <dimension ref="A1:AL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3224,26 +3457,29 @@
     <col width="13.2" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="19.8" customWidth="1" min="16" max="16"/>
-    <col width="17.6" customWidth="1" min="17" max="17"/>
-    <col width="17.6" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="16.5" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="15.4" customWidth="1" min="22" max="22"/>
-    <col width="14.3" customWidth="1" min="23" max="23"/>
+    <col width="14.3" customWidth="1" min="16" max="16"/>
+    <col width="12.1" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="19.8" customWidth="1" min="19" max="19"/>
+    <col width="17.6" customWidth="1" min="20" max="20"/>
+    <col width="17.6" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="16.5" customWidth="1" min="23" max="23"/>
     <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="23.1" customWidth="1" min="25" max="25"/>
-    <col width="23.1" customWidth="1" min="26" max="26"/>
-    <col width="18.7" customWidth="1" min="27" max="27"/>
-    <col width="20.9" customWidth="1" min="28" max="28"/>
-    <col width="19.8" customWidth="1" min="29" max="29"/>
-    <col width="15.4" customWidth="1" min="30" max="30"/>
-    <col width="17.6" customWidth="1" min="31" max="31"/>
-    <col width="10" customWidth="1" min="32" max="32"/>
-    <col width="24.2" customWidth="1" min="33" max="33"/>
-    <col width="20.9" customWidth="1" min="34" max="34"/>
+    <col width="15.4" customWidth="1" min="25" max="25"/>
+    <col width="14.3" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="23.1" customWidth="1" min="28" max="28"/>
+    <col width="23.1" customWidth="1" min="29" max="29"/>
+    <col width="18.7" customWidth="1" min="30" max="30"/>
+    <col width="20.9" customWidth="1" min="31" max="31"/>
+    <col width="19.8" customWidth="1" min="32" max="32"/>
+    <col width="15.4" customWidth="1" min="33" max="33"/>
+    <col width="17.6" customWidth="1" min="34" max="34"/>
     <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="24.2" customWidth="1" min="36" max="36"/>
+    <col width="20.9" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -3319,105 +3555,120 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>CanReload</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>WeaponReqMana</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ManaPerAmmo</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>MaxRange</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>DamageFalloffStart</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>DamageFalloffEnd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>DamageFalloffMin</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>IsHitscan</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ProjectileSpeed</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>CanADS</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ScopeZoomLevel</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>SpreadHipfire</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>SpreadADS</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>SpreadIncreasePerShot</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MaxSpreadBloomHipfire</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MaxSpreadBloomADS</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>SpreadRecoveryDelay</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>SpreadRecoveryRate</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>RecoilVertical</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>RecoilHorizontal</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>ADSSpeed</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>ADSMoveSpeedMultiplier</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>MoveSpeedMultiplier</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>EquipTime</t>
         </is>
@@ -3496,7 +3747,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -3516,34 +3767,34 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>float</t>
@@ -3595,6 +3846,21 @@
         </is>
       </c>
       <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AL2" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -3655,77 +3921,88 @@
       <c r="N3" s="4" t="n">
         <v>1.9</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="4" t="n">
         <v>3500</v>
       </c>
-      <c r="P3" s="4" t="n">
+      <c r="S3" s="4" t="n">
         <v>1200</v>
       </c>
-      <c r="Q3" s="4" t="n">
+      <c r="T3" s="4" t="n">
         <v>3500</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="S3" s="6" t="inlineStr">
+      <c r="V3" s="6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T3" s="4" t="n">
+      <c r="W3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U3" s="6" t="inlineStr">
+      <c r="X3" s="6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="V3" s="4" t="n">
+      <c r="Y3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W3" s="4" t="n">
+      <c r="Z3" s="4" t="n">
         <v>2.5</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="Y3" s="4" t="n">
+      <c r="AB3" s="4" t="n">
         <v>0.4</v>
-      </c>
-      <c r="Z3" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA3" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB3" s="4" t="n">
-        <v>0.1</v>
       </c>
       <c r="AC3" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD3" s="7" t="n">
+      <c r="AD3" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE3" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AF3" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AE3" s="7" t="n">
+      <c r="AH3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AF3" s="4" t="n">
+      <c r="AI3" s="4" t="n">
         <v>0.18</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="AH3" s="4" t="n">
+      <c r="AK3" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="AI3" s="4" t="n">
+      <c r="AL3" s="4" t="n">
         <v>0.35</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="S3 U3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="O3 V3 X3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -3750,7 +4027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ3"/>
+  <dimension ref="A1:AM3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3768,27 +4045,30 @@
     <col width="13.2" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="19.8" customWidth="1" min="16" max="16"/>
-    <col width="17.6" customWidth="1" min="17" max="17"/>
-    <col width="17.6" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="16.5" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="15.4" customWidth="1" min="22" max="22"/>
-    <col width="14.3" customWidth="1" min="23" max="23"/>
+    <col width="14.3" customWidth="1" min="16" max="16"/>
+    <col width="12.1" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="19.8" customWidth="1" min="19" max="19"/>
+    <col width="17.6" customWidth="1" min="20" max="20"/>
+    <col width="17.6" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="16.5" customWidth="1" min="23" max="23"/>
     <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="23.1" customWidth="1" min="25" max="25"/>
-    <col width="23.1" customWidth="1" min="26" max="26"/>
-    <col width="18.7" customWidth="1" min="27" max="27"/>
-    <col width="20.9" customWidth="1" min="28" max="28"/>
-    <col width="19.8" customWidth="1" min="29" max="29"/>
-    <col width="15.4" customWidth="1" min="30" max="30"/>
-    <col width="17.6" customWidth="1" min="31" max="31"/>
-    <col width="10" customWidth="1" min="32" max="32"/>
-    <col width="24.2" customWidth="1" min="33" max="33"/>
-    <col width="20.9" customWidth="1" min="34" max="34"/>
+    <col width="15.4" customWidth="1" min="25" max="25"/>
+    <col width="14.3" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="23.1" customWidth="1" min="28" max="28"/>
+    <col width="23.1" customWidth="1" min="29" max="29"/>
+    <col width="18.7" customWidth="1" min="30" max="30"/>
+    <col width="20.9" customWidth="1" min="31" max="31"/>
+    <col width="19.8" customWidth="1" min="32" max="32"/>
+    <col width="15.4" customWidth="1" min="33" max="33"/>
+    <col width="17.6" customWidth="1" min="34" max="34"/>
     <col width="10" customWidth="1" min="35" max="35"/>
-    <col width="18.7" customWidth="1" min="36" max="36"/>
+    <col width="24.2" customWidth="1" min="36" max="36"/>
+    <col width="20.9" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="18.7" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -3864,110 +4144,125 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>CanReload</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>WeaponReqMana</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ManaPerAmmo</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>MaxRange</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>DamageFalloffStart</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>DamageFalloffEnd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>DamageFalloffMin</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>IsHitscan</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ProjectileSpeed</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>CanADS</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ScopeZoomLevel</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>SpreadHipfire</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>SpreadADS</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>SpreadIncreasePerShot</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MaxSpreadBloomHipfire</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MaxSpreadBloomADS</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>SpreadRecoveryDelay</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>SpreadRecoveryRate</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>RecoilVertical</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>RecoilHorizontal</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>ADSSpeed</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>ADSMoveSpeedMultiplier</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>MoveSpeedMultiplier</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>EquipTime</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>PelletSpreadAngle</t>
         </is>
@@ -4046,7 +4341,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -4066,34 +4361,34 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>float</t>
@@ -4150,6 +4445,21 @@
         </is>
       </c>
       <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AL2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AM2" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -4210,80 +4520,91 @@
       <c r="N3" s="4" t="n">
         <v>2.8</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="4" t="n">
         <v>1500</v>
       </c>
-      <c r="P3" s="4" t="n">
+      <c r="S3" s="4" t="n">
         <v>400</v>
       </c>
-      <c r="Q3" s="4" t="n">
+      <c r="T3" s="4" t="n">
         <v>1500</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="S3" s="6" t="inlineStr">
+      <c r="V3" s="6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T3" s="4" t="n">
+      <c r="W3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U3" s="6" t="inlineStr">
+      <c r="X3" s="6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
-      </c>
-      <c r="V3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W3" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="X3" s="4" t="n">
-        <v>4</v>
       </c>
       <c r="Y3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Z3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA3" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AB3" s="4" t="n">
+      <c r="AE3" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="AC3" s="4" t="n">
+      <c r="AF3" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="AD3" s="7" t="n">
+      <c r="AG3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AE3" s="7" t="n">
+      <c r="AH3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AF3" s="4" t="n">
+      <c r="AI3" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="AH3" s="4" t="n">
+      <c r="AK3" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="AI3" s="4" t="n">
+      <c r="AL3" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="AJ3" s="5" t="n">
+      <c r="AM3" s="5" t="n">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="S3 U3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="O3 V3 X3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -4307,7 +4628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4627,12 +4948,12 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>ReloadTime</t>
+          <t>CanReload</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -4642,14 +4963,14 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>재장전 소요 시간(초).</t>
+          <t>장전 가능 여부. FALSE면 장전 자체가 불가능.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>MaxRange</t>
+          <t>WeaponReqMana</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -4664,14 +4985,14 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>유효 사거리.</t>
+          <t>장전 시 필요 마나(기본 요구치). 프로토타입 기준 MagazineSize와 동일.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>DamageFalloffStart</t>
+          <t>ManaPerAmmo</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -4686,14 +5007,14 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>데미지 감소 시작 거리.</t>
+          <t>탄 1발당 요구 마나 감소분.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>DamageFalloffEnd</t>
+          <t>ReloadTime</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -4708,14 +5029,14 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>최소 데미지로 수렴하는 거리.</t>
+          <t>재장전 소요 시간(초).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>DamageFalloffMin</t>
+          <t>MaxRange</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
@@ -4730,19 +5051,19 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>최소 데미지.</t>
+          <t>유효 사거리.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>IsHitscan</t>
+          <t>DamageFalloffStart</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -4752,14 +5073,14 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>TRUE=히트스캔, FALSE=투사체.</t>
+          <t>데미지 감소 시작 거리.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>ProjectileSpeed</t>
+          <t>DamageFalloffEnd</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
@@ -4774,19 +5095,19 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>투사체 속도.</t>
+          <t>최소 데미지로 수렴하는 거리.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>CanADS</t>
+          <t>DamageFalloffMin</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -4796,19 +5117,19 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>조준(ADS) 가능 여부.</t>
+          <t>최소 데미지.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>ScopeZoomLevel</t>
+          <t>IsHitscan</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
@@ -4818,14 +5139,14 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>조준경 배율. 없으면 1.0.</t>
+          <t>TRUE=히트스캔, FALSE=투사체.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>SpreadHipfire</t>
+          <t>ProjectileSpeed</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -4840,19 +5161,19 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>무조준 탄착 분산도.</t>
+          <t>투사체 속도.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>SpreadADS</t>
+          <t>CanADS</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -4862,14 +5183,14 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>조준 탄착 분산도.</t>
+          <t>조준(ADS) 가능 여부.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>SpreadIncreasePerShot</t>
+          <t>ScopeZoomLevel</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -4884,14 +5205,14 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>발사 1회당 탄퍼짐 증가량.</t>
+          <t>조준경 배율. 없으면 1.0.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>MaxSpreadBloomHipfire</t>
+          <t>SpreadHipfire</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
@@ -4906,14 +5227,14 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>무조준 탄퍼짐 최대치.</t>
+          <t>무조준 탄착 분산도.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>MaxSpreadBloomADS</t>
+          <t>SpreadADS</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -4928,14 +5249,14 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>조준 탄퍼짐 최대치.</t>
+          <t>조준 탄착 분산도.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>SpreadRecoveryDelay</t>
+          <t>SpreadIncreasePerShot</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
@@ -4950,14 +5271,14 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>탄퍼짐 회복 시작 딜레이(초).</t>
+          <t>발사 1회당 탄퍼짐 증가량.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>SpreadRecoveryRate</t>
+          <t>MaxSpreadBloomHipfire</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -4972,14 +5293,14 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>초당 탄퍼짐 감소량.</t>
+          <t>무조준 탄퍼짐 최대치.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>RecoilVertical</t>
+          <t>MaxSpreadBloomADS</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
@@ -4989,19 +5310,19 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>All (예약)</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>미사용.</t>
+          <t>조준 탄퍼짐 최대치.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>RecoilHorizontal</t>
+          <t>SpreadRecoveryDelay</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -5011,19 +5332,19 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>All (예약)</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>미사용.</t>
+          <t>탄퍼짐 회복 시작 딜레이(초).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>ADSSpeed</t>
+          <t>SpreadRecoveryRate</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
@@ -5038,14 +5359,14 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>조준 전환 소요 시간(초).</t>
+          <t>초당 탄퍼짐 감소량.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>ADSMoveSpeedMultiplier</t>
+          <t>RecoilVertical</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -5055,19 +5376,19 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>All (예약)</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>조준 중 이동속도 배율.</t>
+          <t>미사용.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>MoveSpeedMultiplier</t>
+          <t>RecoilHorizontal</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
@@ -5077,19 +5398,19 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>All (예약)</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>장착 중 기본 이동속도 배율.</t>
+          <t>미사용.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>EquipTime</t>
+          <t>ADSSpeed</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -5104,27 +5425,93 @@
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>무기 교체 소요 시간(초).</t>
+          <t>조준 전환 소요 시간(초).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
+          <t>ADSMoveSpeedMultiplier</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>조준 중 이동속도 배율.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>MoveSpeedMultiplier</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>장착 중 기본 이동속도 배율.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>EquipTime</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>무기 교체 소요 시간(초).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
           <t>PelletSpreadAngle</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>ShotGun</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>산탄 퍼짐 각도(도).</t>
         </is>

--- a/Content/Data/WeaponData.xlsx
+++ b/Content/Data/WeaponData.xlsx
@@ -299,42 +299,47 @@
         <t>탄 1발당 요구 마나 감소분. CanReload=FALSE인 무기도 값은 유지(추후 변경 대비).</t>
       </text>
     </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <t>장전 방식: Single(한 발씩 장전) 또는 Magazine(탄창째로 한번에 장전). 값 타입은 string.</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0" shapeId="0">
       <text>
         <t>TRUE=히트스캔, FALSE=투사체.</t>
       </text>
     </comment>
-    <comment ref="X1" authorId="0" shapeId="0">
+    <comment ref="Y1" authorId="0" shapeId="0">
       <text>
         <t>조준(ADS) 가능 여부. FALSE면 이 무기는 조준 자체가 불가능.</t>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0">
+    <comment ref="Z1" authorId="0" shapeId="0">
       <text>
         <t>조준경/가늠자 배율. 조준경 없으면 1.0.</t>
       </text>
     </comment>
-    <comment ref="AC1" authorId="0" shapeId="0">
+    <comment ref="AD1" authorId="0" shapeId="0">
       <text>
         <t>무조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
       </text>
     </comment>
-    <comment ref="AD1" authorId="0" shapeId="0">
+    <comment ref="AE1" authorId="0" shapeId="0">
       <text>
         <t>조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
       </text>
     </comment>
-    <comment ref="AG1" authorId="0" shapeId="0">
+    <comment ref="AH1" authorId="0" shapeId="0">
       <text>
         <t>예약 필드 (현재 미사용). 추후 카메라 반동 전환 시 사용 예정.</t>
       </text>
     </comment>
-    <comment ref="AH1" authorId="0" shapeId="0">
+    <comment ref="AI1" authorId="0" shapeId="0">
       <text>
         <t>예약 필드 (현재 미사용). RecoilVertical과 동일 목적.</t>
       </text>
     </comment>
-    <comment ref="AJ1" authorId="0" shapeId="0">
+    <comment ref="AK1" authorId="0" shapeId="0">
       <text>
         <t>조준(ADS) 중 이동속도 배율. MoveSpeedMultiplier와 별개로 조준 시 추가 적용.</t>
       </text>
@@ -413,42 +418,47 @@
         <t>탄 1발당 요구 마나 감소분. CanReload=FALSE인 무기도 값은 유지(추후 변경 대비).</t>
       </text>
     </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <t>장전 방식: Single(한 발씩 장전) 또는 Magazine(탄창째로 한번에 장전). 값 타입은 string.</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0" shapeId="0">
       <text>
         <t>TRUE=히트스캔, FALSE=투사체.</t>
       </text>
     </comment>
-    <comment ref="X1" authorId="0" shapeId="0">
+    <comment ref="Y1" authorId="0" shapeId="0">
       <text>
         <t>조준(ADS) 가능 여부. FALSE면 이 무기는 조준 자체가 불가능.</t>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0">
+    <comment ref="Z1" authorId="0" shapeId="0">
       <text>
         <t>조준경/가늠자 배율. 조준경 없으면 1.0.</t>
       </text>
     </comment>
-    <comment ref="AC1" authorId="0" shapeId="0">
+    <comment ref="AD1" authorId="0" shapeId="0">
       <text>
         <t>무조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
       </text>
     </comment>
-    <comment ref="AD1" authorId="0" shapeId="0">
+    <comment ref="AE1" authorId="0" shapeId="0">
       <text>
         <t>조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
       </text>
     </comment>
-    <comment ref="AG1" authorId="0" shapeId="0">
+    <comment ref="AH1" authorId="0" shapeId="0">
       <text>
         <t>예약 필드 (현재 미사용). 추후 카메라 반동 전환 시 사용 예정.</t>
       </text>
     </comment>
-    <comment ref="AH1" authorId="0" shapeId="0">
+    <comment ref="AI1" authorId="0" shapeId="0">
       <text>
         <t>예약 필드 (현재 미사용). RecoilVertical과 동일 목적.</t>
       </text>
     </comment>
-    <comment ref="AJ1" authorId="0" shapeId="0">
+    <comment ref="AK1" authorId="0" shapeId="0">
       <text>
         <t>조준(ADS) 중 이동속도 배율. MoveSpeedMultiplier와 별개로 조준 시 추가 적용.</t>
       </text>
@@ -527,42 +537,47 @@
         <t>탄 1발당 요구 마나 감소분. CanReload=FALSE인 무기도 값은 유지(추후 변경 대비).</t>
       </text>
     </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <t>장전 방식: Single(한 발씩 장전) 또는 Magazine(탄창째로 한번에 장전). 값 타입은 string.</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0" shapeId="0">
       <text>
         <t>TRUE=히트스캔, FALSE=투사체.</t>
       </text>
     </comment>
-    <comment ref="X1" authorId="0" shapeId="0">
+    <comment ref="Y1" authorId="0" shapeId="0">
       <text>
         <t>조준(ADS) 가능 여부. FALSE면 이 무기는 조준 자체가 불가능.</t>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0">
+    <comment ref="Z1" authorId="0" shapeId="0">
       <text>
         <t>조준경/가늠자 배율. 조준경 없으면 1.0.</t>
       </text>
     </comment>
-    <comment ref="AC1" authorId="0" shapeId="0">
+    <comment ref="AD1" authorId="0" shapeId="0">
       <text>
         <t>무조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
       </text>
     </comment>
-    <comment ref="AD1" authorId="0" shapeId="0">
+    <comment ref="AE1" authorId="0" shapeId="0">
       <text>
         <t>조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
       </text>
     </comment>
-    <comment ref="AG1" authorId="0" shapeId="0">
+    <comment ref="AH1" authorId="0" shapeId="0">
       <text>
         <t>예약 필드 (현재 미사용). 추후 카메라 반동 전환 시 사용 예정.</t>
       </text>
     </comment>
-    <comment ref="AH1" authorId="0" shapeId="0">
+    <comment ref="AI1" authorId="0" shapeId="0">
       <text>
         <t>예약 필드 (현재 미사용). RecoilVertical과 동일 목적.</t>
       </text>
     </comment>
-    <comment ref="AJ1" authorId="0" shapeId="0">
+    <comment ref="AK1" authorId="0" shapeId="0">
       <text>
         <t>조준(ADS) 중 이동속도 배율. MoveSpeedMultiplier와 별개로 조준 시 추가 적용.</t>
       </text>
@@ -641,42 +656,47 @@
         <t>탄 1발당 요구 마나 감소분. CanReload=FALSE인 무기도 값은 유지(추후 변경 대비).</t>
       </text>
     </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <t>장전 방식: Single(한 발씩 장전) 또는 Magazine(탄창째로 한번에 장전). 값 타입은 string.</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0" shapeId="0">
       <text>
         <t>TRUE=히트스캔, FALSE=투사체.</t>
       </text>
     </comment>
-    <comment ref="X1" authorId="0" shapeId="0">
+    <comment ref="Y1" authorId="0" shapeId="0">
       <text>
         <t>조준(ADS) 가능 여부. FALSE면 이 무기는 조준 자체가 불가능.</t>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0">
+    <comment ref="Z1" authorId="0" shapeId="0">
       <text>
         <t>조준경/가늠자 배율. 조준경 없으면 1.0.</t>
       </text>
     </comment>
-    <comment ref="AC1" authorId="0" shapeId="0">
+    <comment ref="AD1" authorId="0" shapeId="0">
       <text>
         <t>무조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
       </text>
     </comment>
-    <comment ref="AD1" authorId="0" shapeId="0">
+    <comment ref="AE1" authorId="0" shapeId="0">
       <text>
         <t>조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
       </text>
     </comment>
-    <comment ref="AG1" authorId="0" shapeId="0">
+    <comment ref="AH1" authorId="0" shapeId="0">
       <text>
         <t>예약 필드 (현재 미사용). 추후 카메라 반동 전환 시 사용 예정.</t>
       </text>
     </comment>
-    <comment ref="AH1" authorId="0" shapeId="0">
+    <comment ref="AI1" authorId="0" shapeId="0">
       <text>
         <t>예약 필드 (현재 미사용). RecoilVertical과 동일 목적.</t>
       </text>
     </comment>
-    <comment ref="AJ1" authorId="0" shapeId="0">
+    <comment ref="AK1" authorId="0" shapeId="0">
       <text>
         <t>조준(ADS) 중 이동속도 배율. MoveSpeedMultiplier와 별개로 조준 시 추가 적용.</t>
       </text>
@@ -755,42 +775,47 @@
         <t>탄 1발당 요구 마나 감소분. CanReload=FALSE인 무기도 값은 유지(추후 변경 대비).</t>
       </text>
     </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <t>장전 방식: Single(한 발씩 장전) 또는 Magazine(탄창째로 한번에 장전). 값 타입은 string.</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0" shapeId="0">
       <text>
         <t>TRUE=히트스캔, FALSE=투사체.</t>
       </text>
     </comment>
-    <comment ref="X1" authorId="0" shapeId="0">
+    <comment ref="Y1" authorId="0" shapeId="0">
       <text>
         <t>조준(ADS) 가능 여부. FALSE면 이 무기는 조준 자체가 불가능.</t>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0">
+    <comment ref="Z1" authorId="0" shapeId="0">
       <text>
         <t>조준경/가늠자 배율. 조준경 없으면 1.0.</t>
       </text>
     </comment>
-    <comment ref="AC1" authorId="0" shapeId="0">
+    <comment ref="AD1" authorId="0" shapeId="0">
       <text>
         <t>무조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
       </text>
     </comment>
-    <comment ref="AD1" authorId="0" shapeId="0">
+    <comment ref="AE1" authorId="0" shapeId="0">
       <text>
         <t>조준 상태에서 탄퍼짐이 도달할 수 있는 최대치.</t>
       </text>
     </comment>
-    <comment ref="AG1" authorId="0" shapeId="0">
+    <comment ref="AH1" authorId="0" shapeId="0">
       <text>
         <t>예약 필드 (현재 미사용). 추후 카메라 반동 전환 시 사용 예정.</t>
       </text>
     </comment>
-    <comment ref="AH1" authorId="0" shapeId="0">
+    <comment ref="AI1" authorId="0" shapeId="0">
       <text>
         <t>예약 필드 (현재 미사용). RecoilVertical과 동일 목적.</t>
       </text>
     </comment>
-    <comment ref="AJ1" authorId="0" shapeId="0">
+    <comment ref="AK1" authorId="0" shapeId="0">
       <text>
         <t>조준(ADS) 중 이동속도 배율. MoveSpeedMultiplier와 별개로 조준 시 추가 적용.</t>
       </text>
@@ -1541,7 +1566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL3"/>
+  <dimension ref="A1:AM3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1561,27 +1586,28 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="14.3" customWidth="1" min="16" max="16"/>
     <col width="12.1" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="19.8" customWidth="1" min="19" max="19"/>
-    <col width="17.6" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="19.8" customWidth="1" min="20" max="20"/>
     <col width="17.6" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="16.5" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="15.4" customWidth="1" min="25" max="25"/>
-    <col width="14.3" customWidth="1" min="26" max="26"/>
-    <col width="10" customWidth="1" min="27" max="27"/>
-    <col width="23.1" customWidth="1" min="28" max="28"/>
+    <col width="17.6" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="16.5" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="15.4" customWidth="1" min="26" max="26"/>
+    <col width="14.3" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
     <col width="23.1" customWidth="1" min="29" max="29"/>
-    <col width="18.7" customWidth="1" min="30" max="30"/>
-    <col width="20.9" customWidth="1" min="31" max="31"/>
-    <col width="19.8" customWidth="1" min="32" max="32"/>
-    <col width="15.4" customWidth="1" min="33" max="33"/>
-    <col width="17.6" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
-    <col width="24.2" customWidth="1" min="36" max="36"/>
-    <col width="20.9" customWidth="1" min="37" max="37"/>
-    <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="23.1" customWidth="1" min="30" max="30"/>
+    <col width="18.7" customWidth="1" min="31" max="31"/>
+    <col width="20.9" customWidth="1" min="32" max="32"/>
+    <col width="19.8" customWidth="1" min="33" max="33"/>
+    <col width="15.4" customWidth="1" min="34" max="34"/>
+    <col width="17.6" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="24.2" customWidth="1" min="37" max="37"/>
+    <col width="20.9" customWidth="1" min="38" max="38"/>
+    <col width="10" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -1672,105 +1698,110 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>ReloadType</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>MaxRange</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>DamageFalloffStart</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>DamageFalloffEnd</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>DamageFalloffMin</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>IsHitscan</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ProjectileSpeed</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>CanADS</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>ScopeZoomLevel</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>SpreadHipfire</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>SpreadADS</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>SpreadIncreasePerShot</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MaxSpreadBloomHipfire</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MaxSpreadBloomADS</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>SpreadRecoveryDelay</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>SpreadRecoveryRate</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>RecoilVertical</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>RecoilHorizontal</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>ADSSpeed</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>ADSMoveSpeedMultiplier</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>MoveSpeedMultiplier</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>EquipTime</t>
         </is>
@@ -1864,7 +1895,7 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
@@ -1884,24 +1915,24 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>float</t>
@@ -1963,6 +1994,11 @@
         </is>
       </c>
       <c r="AL2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AM2" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -2034,77 +2070,82 @@
       <c r="Q3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>Magazine</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="n">
         <v>3000</v>
       </c>
-      <c r="S3" s="4" t="n">
+      <c r="T3" s="4" t="n">
         <v>1500</v>
       </c>
-      <c r="T3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>3000</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="V3" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="V3" s="6" t="inlineStr">
+      <c r="W3" s="6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="W3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="X3" s="6" t="inlineStr">
+      <c r="Y3" s="6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y3" s="4" t="n">
+      <c r="Z3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>3.5</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AB3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="AB3" s="4" t="n">
+      <c r="AC3" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="AC3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AE3" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AE3" s="4" t="n">
+      <c r="AF3" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="AF3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="AG3" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="AH3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AI3" s="4" t="n">
+      <c r="AI3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AK3" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="AK3" s="4" t="n">
+      <c r="AL3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="AL3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>0.4</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation sqref="O3 V3 X3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+  <dataValidations count="5">
+    <dataValidation sqref="O3 W3 Y3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -2115,6 +2156,9 @@
     </dataValidation>
     <dataValidation sqref="J3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Single,Burst,FullAuto"</formula1>
+    </dataValidation>
+    <dataValidation sqref="R3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Single,Magazine"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2129,7 +2173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL4"/>
+  <dimension ref="A1:AM4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2149,27 +2193,28 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="14.3" customWidth="1" min="16" max="16"/>
     <col width="12.1" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="19.8" customWidth="1" min="19" max="19"/>
-    <col width="17.6" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="19.8" customWidth="1" min="20" max="20"/>
     <col width="17.6" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="16.5" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="15.4" customWidth="1" min="25" max="25"/>
-    <col width="14.3" customWidth="1" min="26" max="26"/>
-    <col width="10" customWidth="1" min="27" max="27"/>
-    <col width="23.1" customWidth="1" min="28" max="28"/>
+    <col width="17.6" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="16.5" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="15.4" customWidth="1" min="26" max="26"/>
+    <col width="14.3" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
     <col width="23.1" customWidth="1" min="29" max="29"/>
-    <col width="18.7" customWidth="1" min="30" max="30"/>
-    <col width="20.9" customWidth="1" min="31" max="31"/>
-    <col width="19.8" customWidth="1" min="32" max="32"/>
-    <col width="15.4" customWidth="1" min="33" max="33"/>
-    <col width="17.6" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
-    <col width="24.2" customWidth="1" min="36" max="36"/>
-    <col width="20.9" customWidth="1" min="37" max="37"/>
-    <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="23.1" customWidth="1" min="30" max="30"/>
+    <col width="18.7" customWidth="1" min="31" max="31"/>
+    <col width="20.9" customWidth="1" min="32" max="32"/>
+    <col width="19.8" customWidth="1" min="33" max="33"/>
+    <col width="15.4" customWidth="1" min="34" max="34"/>
+    <col width="17.6" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="24.2" customWidth="1" min="37" max="37"/>
+    <col width="20.9" customWidth="1" min="38" max="38"/>
+    <col width="10" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -2260,105 +2305,110 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>ReloadType</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>MaxRange</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>DamageFalloffStart</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>DamageFalloffEnd</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>DamageFalloffMin</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>IsHitscan</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ProjectileSpeed</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>CanADS</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>ScopeZoomLevel</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>SpreadHipfire</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>SpreadADS</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>SpreadIncreasePerShot</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MaxSpreadBloomHipfire</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MaxSpreadBloomADS</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>SpreadRecoveryDelay</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>SpreadRecoveryRate</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>RecoilVertical</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>RecoilHorizontal</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>ADSSpeed</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>ADSMoveSpeedMultiplier</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>MoveSpeedMultiplier</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>EquipTime</t>
         </is>
@@ -2452,7 +2502,7 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
@@ -2472,24 +2522,24 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>float</t>
@@ -2551,6 +2601,11 @@
         </is>
       </c>
       <c r="AL2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AM2" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -2622,71 +2677,76 @@
       <c r="Q3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>Magazine</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="n">
         <v>6000</v>
       </c>
-      <c r="S3" s="4" t="n">
+      <c r="T3" s="4" t="n">
         <v>3000</v>
       </c>
-      <c r="T3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>6000</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="V3" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="V3" s="6" t="inlineStr">
+      <c r="W3" s="6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="W3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="X3" s="6" t="inlineStr">
+      <c r="Y3" s="6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y3" s="4" t="n">
+      <c r="Z3" s="4" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AB3" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="AB3" s="4" t="n">
+      <c r="AC3" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AE3" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="AE3" s="4" t="n">
+      <c r="AF3" s="4" t="n">
         <v>0.15</v>
       </c>
-      <c r="AF3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>5</v>
-      </c>
-      <c r="AG3" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="AH3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AI3" s="4" t="n">
+      <c r="AI3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AK3" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="AK3" s="4" t="n">
+      <c r="AL3" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="AL3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -2756,77 +2816,82 @@
       <c r="Q4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="R4" s="4" t="n">
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>Magazine</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="n">
         <v>6500</v>
       </c>
-      <c r="S4" s="4" t="n">
+      <c r="T4" s="4" t="n">
         <v>3200</v>
       </c>
-      <c r="T4" s="4" t="n">
+      <c r="U4" s="4" t="n">
         <v>6500</v>
       </c>
-      <c r="U4" s="4" t="n">
+      <c r="V4" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="V4" s="6" t="inlineStr">
+      <c r="W4" s="6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="W4" s="4" t="n">
+      <c r="X4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="X4" s="6" t="inlineStr">
+      <c r="Y4" s="6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="n">
+      <c r="Z4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Z4" s="4" t="n">
+      <c r="AA4" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="AA4" s="4" t="n">
+      <c r="AB4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="AB4" s="4" t="n">
+      <c r="AC4" s="4" t="n">
         <v>0.6</v>
       </c>
-      <c r="AC4" s="4" t="n">
+      <c r="AD4" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="AD4" s="4" t="n">
+      <c r="AE4" s="4" t="n">
         <v>3.5</v>
       </c>
-      <c r="AE4" s="4" t="n">
+      <c r="AF4" s="4" t="n">
         <v>0.15</v>
       </c>
-      <c r="AF4" s="4" t="n">
+      <c r="AG4" s="4" t="n">
         <v>5.5</v>
-      </c>
-      <c r="AG4" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="AH4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AI4" s="4" t="n">
+      <c r="AI4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="4" t="n">
         <v>0.22</v>
       </c>
-      <c r="AJ4" s="4" t="n">
+      <c r="AK4" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="AK4" s="4" t="n">
+      <c r="AL4" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="AL4" s="4" t="n">
+      <c r="AM4" s="4" t="n">
         <v>0.55</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation sqref="O3:O4 V3:V4 X3:X4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+  <dataValidations count="5">
+    <dataValidation sqref="O3:O4 W3:W4 Y3:Y4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation sqref="B3:B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -2838,6 +2903,9 @@
     <dataValidation sqref="J3:J4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Single,Burst,FullAuto"</formula1>
     </dataValidation>
+    <dataValidation sqref="R3:R4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Single,Magazine"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -2848,1182 +2916,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AL3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12.1" customWidth="1" min="7" max="7"/>
-    <col width="19.8" customWidth="1" min="8" max="8"/>
-    <col width="13.2" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="18.7" customWidth="1" min="12" max="12"/>
-    <col width="13.2" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="14.3" customWidth="1" min="16" max="16"/>
-    <col width="12.1" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="19.8" customWidth="1" min="19" max="19"/>
-    <col width="17.6" customWidth="1" min="20" max="20"/>
-    <col width="17.6" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="16.5" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="15.4" customWidth="1" min="25" max="25"/>
-    <col width="14.3" customWidth="1" min="26" max="26"/>
-    <col width="10" customWidth="1" min="27" max="27"/>
-    <col width="23.1" customWidth="1" min="28" max="28"/>
-    <col width="23.1" customWidth="1" min="29" max="29"/>
-    <col width="18.7" customWidth="1" min="30" max="30"/>
-    <col width="20.9" customWidth="1" min="31" max="31"/>
-    <col width="19.8" customWidth="1" min="32" max="32"/>
-    <col width="15.4" customWidth="1" min="33" max="33"/>
-    <col width="17.6" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
-    <col width="24.2" customWidth="1" min="36" max="36"/>
-    <col width="20.9" customWidth="1" min="37" max="37"/>
-    <col width="10" customWidth="1" min="38" max="38"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Index</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>WeaponType</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Rarity</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>NameKey</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DescKey</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Damage</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>PelletCount</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>HeadshotMultiplier</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>FireRate_RPS</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>FireMode</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>BurstCount</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>BurstShotInterval</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>MagazineSize</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>ReloadTime</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>CanReload</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>WeaponReqMana</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>ManaPerAmmo</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>MaxRange</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>DamageFalloffStart</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>DamageFalloffEnd</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>DamageFalloffMin</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>IsHitscan</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>ProjectileSpeed</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>CanADS</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>ScopeZoomLevel</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>SpreadHipfire</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>SpreadADS</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>SpreadIncreasePerShot</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>MaxSpreadBloomHipfire</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>MaxSpreadBloomADS</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>SpreadRecoveryDelay</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>SpreadRecoveryRate</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>RecoilVertical</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>RecoilHorizontal</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>ADSSpeed</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>ADSMoveSpeedMultiplier</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>MoveSpeedMultiplier</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>EquipTime</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AF2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AG2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AH2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AI2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AJ2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AK2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AL2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>SR_1</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>SniperRifle</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>SR_1.Name</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>SR_1.Description</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="K3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O3" s="6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" s="4" t="n">
-        <v>15000</v>
-      </c>
-      <c r="S3" s="4" t="n">
-        <v>8000</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>15000</v>
-      </c>
-      <c r="U3" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="V3" s="6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" s="6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="Y3" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z3" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA3" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AB3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC3" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE3" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF3" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG3" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="4" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AJ3" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK3" s="4" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="AL3" s="4" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="4">
-    <dataValidation sqref="O3 V3 X3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"SniperRifle"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Common,Rare,Epic"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Single,Burst,FullAuto"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00BF8F00"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AL3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12.1" customWidth="1" min="7" max="7"/>
-    <col width="19.8" customWidth="1" min="8" max="8"/>
-    <col width="13.2" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="18.7" customWidth="1" min="12" max="12"/>
-    <col width="13.2" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="14.3" customWidth="1" min="16" max="16"/>
-    <col width="12.1" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="19.8" customWidth="1" min="19" max="19"/>
-    <col width="17.6" customWidth="1" min="20" max="20"/>
-    <col width="17.6" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="16.5" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="15.4" customWidth="1" min="25" max="25"/>
-    <col width="14.3" customWidth="1" min="26" max="26"/>
-    <col width="10" customWidth="1" min="27" max="27"/>
-    <col width="23.1" customWidth="1" min="28" max="28"/>
-    <col width="23.1" customWidth="1" min="29" max="29"/>
-    <col width="18.7" customWidth="1" min="30" max="30"/>
-    <col width="20.9" customWidth="1" min="31" max="31"/>
-    <col width="19.8" customWidth="1" min="32" max="32"/>
-    <col width="15.4" customWidth="1" min="33" max="33"/>
-    <col width="17.6" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
-    <col width="24.2" customWidth="1" min="36" max="36"/>
-    <col width="20.9" customWidth="1" min="37" max="37"/>
-    <col width="10" customWidth="1" min="38" max="38"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Index</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>WeaponType</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Rarity</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>NameKey</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DescKey</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Damage</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>PelletCount</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>HeadshotMultiplier</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>FireRate_RPS</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>FireMode</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>BurstCount</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>BurstShotInterval</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>MagazineSize</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>ReloadTime</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>CanReload</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>WeaponReqMana</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>ManaPerAmmo</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>MaxRange</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>DamageFalloffStart</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>DamageFalloffEnd</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>DamageFalloffMin</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>IsHitscan</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>ProjectileSpeed</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>CanADS</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>ScopeZoomLevel</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>SpreadHipfire</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>SpreadADS</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>SpreadIncreasePerShot</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>MaxSpreadBloomHipfire</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>MaxSpreadBloomADS</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>SpreadRecoveryDelay</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>SpreadRecoveryRate</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>RecoilVertical</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>RecoilHorizontal</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>ADSSpeed</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>ADSMoveSpeedMultiplier</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>MoveSpeedMultiplier</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>EquipTime</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AF2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AG2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AH2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AI2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AJ2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AK2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AL2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>SMG_1</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>SubMachineGun</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>SMG_1.Name</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>SMG_1.Description</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>FullAuto</t>
-        </is>
-      </c>
-      <c r="K3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O3" s="6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" s="4" t="n">
-        <v>3500</v>
-      </c>
-      <c r="S3" s="4" t="n">
-        <v>1200</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>3500</v>
-      </c>
-      <c r="U3" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="V3" s="6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" s="6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="Y3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA3" s="4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AB3" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC3" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD3" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE3" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AF3" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG3" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="4" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AJ3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK3" s="4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AL3" s="4" t="n">
-        <v>0.35</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="4">
-    <dataValidation sqref="O3 V3 X3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"SubMachineGun"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Common,Rare,Epic"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Single,Burst,FullAuto"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -4047,28 +2939,28 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="14.3" customWidth="1" min="16" max="16"/>
     <col width="12.1" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="19.8" customWidth="1" min="19" max="19"/>
-    <col width="17.6" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="19.8" customWidth="1" min="20" max="20"/>
     <col width="17.6" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="16.5" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="15.4" customWidth="1" min="25" max="25"/>
-    <col width="14.3" customWidth="1" min="26" max="26"/>
-    <col width="10" customWidth="1" min="27" max="27"/>
-    <col width="23.1" customWidth="1" min="28" max="28"/>
+    <col width="17.6" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="16.5" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="15.4" customWidth="1" min="26" max="26"/>
+    <col width="14.3" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
     <col width="23.1" customWidth="1" min="29" max="29"/>
-    <col width="18.7" customWidth="1" min="30" max="30"/>
-    <col width="20.9" customWidth="1" min="31" max="31"/>
-    <col width="19.8" customWidth="1" min="32" max="32"/>
-    <col width="15.4" customWidth="1" min="33" max="33"/>
-    <col width="17.6" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
-    <col width="24.2" customWidth="1" min="36" max="36"/>
-    <col width="20.9" customWidth="1" min="37" max="37"/>
-    <col width="10" customWidth="1" min="38" max="38"/>
-    <col width="18.7" customWidth="1" min="39" max="39"/>
+    <col width="23.1" customWidth="1" min="30" max="30"/>
+    <col width="18.7" customWidth="1" min="31" max="31"/>
+    <col width="20.9" customWidth="1" min="32" max="32"/>
+    <col width="19.8" customWidth="1" min="33" max="33"/>
+    <col width="15.4" customWidth="1" min="34" max="34"/>
+    <col width="17.6" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="24.2" customWidth="1" min="37" max="37"/>
+    <col width="20.9" customWidth="1" min="38" max="38"/>
+    <col width="10" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -4159,112 +3051,112 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>ReloadType</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>MaxRange</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>DamageFalloffStart</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>DamageFalloffEnd</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>DamageFalloffMin</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>IsHitscan</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ProjectileSpeed</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>CanADS</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>ScopeZoomLevel</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>SpreadHipfire</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>SpreadADS</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>SpreadIncreasePerShot</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MaxSpreadBloomHipfire</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MaxSpreadBloomADS</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>SpreadRecoveryDelay</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>SpreadRecoveryRate</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>RecoilVertical</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>RecoilHorizontal</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>ADSSpeed</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>ADSMoveSpeedMultiplier</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>MoveSpeedMultiplier</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>EquipTime</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>PelletSpreadAngle</t>
         </is>
       </c>
     </row>
@@ -4356,7 +3248,7 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
@@ -4376,22 +3268,22 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
           <t>bool</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -4468,6 +3360,1231 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>SR_1</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>SniperRifle</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>SR_1.Name</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>SR_1.Description</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>Magazine</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="W3" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="X3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA3" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB3" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AC3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD3" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF3" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG3" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AK3" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL3" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AM3" s="4" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="5">
+    <dataValidation sqref="O3 W3 Y3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"SniperRifle"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Common,Rare,Epic"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Single,Burst,FullAuto"</formula1>
+    </dataValidation>
+    <dataValidation sqref="R3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Single,Magazine"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00BF8F00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AM3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12.1" customWidth="1" min="7" max="7"/>
+    <col width="19.8" customWidth="1" min="8" max="8"/>
+    <col width="13.2" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="18.7" customWidth="1" min="12" max="12"/>
+    <col width="13.2" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="14.3" customWidth="1" min="16" max="16"/>
+    <col width="12.1" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="19.8" customWidth="1" min="20" max="20"/>
+    <col width="17.6" customWidth="1" min="21" max="21"/>
+    <col width="17.6" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="16.5" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="15.4" customWidth="1" min="26" max="26"/>
+    <col width="14.3" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="23.1" customWidth="1" min="29" max="29"/>
+    <col width="23.1" customWidth="1" min="30" max="30"/>
+    <col width="18.7" customWidth="1" min="31" max="31"/>
+    <col width="20.9" customWidth="1" min="32" max="32"/>
+    <col width="19.8" customWidth="1" min="33" max="33"/>
+    <col width="15.4" customWidth="1" min="34" max="34"/>
+    <col width="17.6" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="24.2" customWidth="1" min="37" max="37"/>
+    <col width="20.9" customWidth="1" min="38" max="38"/>
+    <col width="10" customWidth="1" min="39" max="39"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>WeaponType</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Rarity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>NameKey</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>DescKey</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>PelletCount</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>HeadshotMultiplier</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>FireRate_RPS</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>FireMode</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>BurstCount</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>BurstShotInterval</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>MagazineSize</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ReloadTime</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>CanReload</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>WeaponReqMana</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ManaPerAmmo</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ReloadType</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>MaxRange</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>DamageFalloffStart</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>DamageFalloffEnd</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>DamageFalloffMin</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>IsHitscan</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ProjectileSpeed</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>CanADS</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ScopeZoomLevel</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>SpreadHipfire</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>SpreadADS</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>SpreadIncreasePerShot</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>MaxSpreadBloomHipfire</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>MaxSpreadBloomADS</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>SpreadRecoveryDelay</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>SpreadRecoveryRate</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>RecoilVertical</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>RecoilHorizontal</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>ADSSpeed</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>ADSMoveSpeedMultiplier</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>MoveSpeedMultiplier</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>EquipTime</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AL2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AM2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>SMG_1</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>SubMachineGun</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>SMG_1.Name</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>SMG_1.Description</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>FullAuto</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>Magazine</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>3500</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>3500</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="W3" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="X3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB3" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC3" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD3" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE3" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF3" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG3" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AK3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL3" s="4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AM3" s="4" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="5">
+    <dataValidation sqref="O3 W3 Y3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"SubMachineGun"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Common,Rare,Epic"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Single,Burst,FullAuto"</formula1>
+    </dataValidation>
+    <dataValidation sqref="R3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Single,Magazine"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AN3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12.1" customWidth="1" min="7" max="7"/>
+    <col width="19.8" customWidth="1" min="8" max="8"/>
+    <col width="13.2" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="18.7" customWidth="1" min="12" max="12"/>
+    <col width="13.2" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="14.3" customWidth="1" min="16" max="16"/>
+    <col width="12.1" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="19.8" customWidth="1" min="20" max="20"/>
+    <col width="17.6" customWidth="1" min="21" max="21"/>
+    <col width="17.6" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="16.5" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="15.4" customWidth="1" min="26" max="26"/>
+    <col width="14.3" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="23.1" customWidth="1" min="29" max="29"/>
+    <col width="23.1" customWidth="1" min="30" max="30"/>
+    <col width="18.7" customWidth="1" min="31" max="31"/>
+    <col width="20.9" customWidth="1" min="32" max="32"/>
+    <col width="19.8" customWidth="1" min="33" max="33"/>
+    <col width="15.4" customWidth="1" min="34" max="34"/>
+    <col width="17.6" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="24.2" customWidth="1" min="37" max="37"/>
+    <col width="20.9" customWidth="1" min="38" max="38"/>
+    <col width="10" customWidth="1" min="39" max="39"/>
+    <col width="18.7" customWidth="1" min="40" max="40"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>WeaponType</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Rarity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>NameKey</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>DescKey</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>PelletCount</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>HeadshotMultiplier</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>FireRate_RPS</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>FireMode</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>BurstCount</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>BurstShotInterval</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>MagazineSize</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ReloadTime</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>CanReload</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>WeaponReqMana</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ManaPerAmmo</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ReloadType</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>MaxRange</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>DamageFalloffStart</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>DamageFalloffEnd</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>DamageFalloffMin</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>IsHitscan</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ProjectileSpeed</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>CanADS</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ScopeZoomLevel</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>SpreadHipfire</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>SpreadADS</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>SpreadIncreasePerShot</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>MaxSpreadBloomHipfire</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>MaxSpreadBloomADS</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>SpreadRecoveryDelay</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>SpreadRecoveryRate</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>RecoilVertical</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>RecoilHorizontal</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>ADSSpeed</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>ADSMoveSpeedMultiplier</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>MoveSpeedMultiplier</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>EquipTime</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>PelletSpreadAngle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AL2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AM2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AN2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>SG_1</t>
         </is>
       </c>
@@ -4531,80 +4648,85 @@
       <c r="Q3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="n">
         <v>1500</v>
       </c>
-      <c r="S3" s="4" t="n">
+      <c r="T3" s="4" t="n">
         <v>400</v>
       </c>
-      <c r="T3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>1500</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="V3" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="V3" s="6" t="inlineStr">
+      <c r="W3" s="6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="W3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="X3" s="6" t="inlineStr">
+      <c r="Y3" s="6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y3" s="4" t="n">
+      <c r="Z3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AB3" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="AB3" s="4" t="n">
+      <c r="AC3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="AC3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AE3" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AE3" s="4" t="n">
+      <c r="AF3" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="AF3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="AG3" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="AH3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AI3" s="4" t="n">
+      <c r="AI3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AK3" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="AK3" s="4" t="n">
+      <c r="AL3" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="AL3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="AM3" s="5" t="n">
+      <c r="AN3" s="5" t="n">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation sqref="O3 V3 X3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+  <dataValidations count="5">
+    <dataValidation sqref="O3 W3 Y3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -4615,6 +4737,9 @@
     </dataValidation>
     <dataValidation sqref="J3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Single,Burst,FullAuto"</formula1>
+    </dataValidation>
+    <dataValidation sqref="R3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Single,Magazine"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4628,7 +4753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5014,12 +5139,12 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>ReloadTime</t>
+          <t>ReloadType</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -5029,14 +5154,14 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>재장전 소요 시간(초).</t>
+          <t>장전 방식: Single(한 발씩) 또는 Magazine(탄창째로 한번에). ShotGun만 Single.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>MaxRange</t>
+          <t>ReloadTime</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
@@ -5051,14 +5176,14 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>유효 사거리.</t>
+          <t>재장전 소요 시간(초).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>DamageFalloffStart</t>
+          <t>MaxRange</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -5073,14 +5198,14 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>데미지 감소 시작 거리.</t>
+          <t>유효 사거리.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>DamageFalloffEnd</t>
+          <t>DamageFalloffStart</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
@@ -5095,14 +5220,14 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>최소 데미지로 수렴하는 거리.</t>
+          <t>데미지 감소 시작 거리.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>DamageFalloffMin</t>
+          <t>DamageFalloffEnd</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -5117,19 +5242,19 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>최소 데미지.</t>
+          <t>최소 데미지로 수렴하는 거리.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>IsHitscan</t>
+          <t>DamageFalloffMin</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
@@ -5139,19 +5264,19 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>TRUE=히트스캔, FALSE=투사체.</t>
+          <t>최소 데미지.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>ProjectileSpeed</t>
+          <t>IsHitscan</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -5161,19 +5286,19 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>투사체 속도.</t>
+          <t>TRUE=히트스캔, FALSE=투사체.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>CanADS</t>
+          <t>ProjectileSpeed</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -5183,19 +5308,19 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>조준(ADS) 가능 여부.</t>
+          <t>투사체 속도.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>ScopeZoomLevel</t>
+          <t>CanADS</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -5205,14 +5330,14 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>조준경 배율. 없으면 1.0.</t>
+          <t>조준(ADS) 가능 여부.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>SpreadHipfire</t>
+          <t>ScopeZoomLevel</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
@@ -5227,14 +5352,14 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>무조준 탄착 분산도.</t>
+          <t>조준경 배율. 없으면 1.0.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>SpreadADS</t>
+          <t>SpreadHipfire</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -5249,14 +5374,14 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>조준 탄착 분산도.</t>
+          <t>무조준 탄착 분산도.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>SpreadIncreasePerShot</t>
+          <t>SpreadADS</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
@@ -5271,14 +5396,14 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>발사 1회당 탄퍼짐 증가량.</t>
+          <t>조준 탄착 분산도.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>MaxSpreadBloomHipfire</t>
+          <t>SpreadIncreasePerShot</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -5293,14 +5418,14 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>무조준 탄퍼짐 최대치.</t>
+          <t>발사 1회당 탄퍼짐 증가량.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>MaxSpreadBloomADS</t>
+          <t>MaxSpreadBloomHipfire</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
@@ -5315,14 +5440,14 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>조준 탄퍼짐 최대치.</t>
+          <t>무조준 탄퍼짐 최대치.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>SpreadRecoveryDelay</t>
+          <t>MaxSpreadBloomADS</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -5337,14 +5462,14 @@
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>탄퍼짐 회복 시작 딜레이(초).</t>
+          <t>조준 탄퍼짐 최대치.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>SpreadRecoveryRate</t>
+          <t>SpreadRecoveryDelay</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
@@ -5359,14 +5484,14 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>초당 탄퍼짐 감소량.</t>
+          <t>탄퍼짐 회복 시작 딜레이(초).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>RecoilVertical</t>
+          <t>SpreadRecoveryRate</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -5376,19 +5501,19 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>All (예약)</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>미사용.</t>
+          <t>초당 탄퍼짐 감소량.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>RecoilHorizontal</t>
+          <t>RecoilVertical</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
@@ -5410,7 +5535,7 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>ADSSpeed</t>
+          <t>RecoilHorizontal</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -5420,19 +5545,19 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>All (예약)</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>조준 전환 소요 시간(초).</t>
+          <t>미사용.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>ADSMoveSpeedMultiplier</t>
+          <t>ADSSpeed</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
@@ -5447,14 +5572,14 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>조준 중 이동속도 배율.</t>
+          <t>조준 전환 소요 시간(초).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>MoveSpeedMultiplier</t>
+          <t>ADSMoveSpeedMultiplier</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -5469,14 +5594,14 @@
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>장착 중 기본 이동속도 배율.</t>
+          <t>조준 중 이동속도 배율.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>EquipTime</t>
+          <t>MoveSpeedMultiplier</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
@@ -5491,27 +5616,49 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>무기 교체 소요 시간(초).</t>
+          <t>장착 중 기본 이동속도 배율.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
+          <t>EquipTime</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>무기 교체 소요 시간(초).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
           <t>PelletSpreadAngle</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>ShotGun</t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr">
+      <c r="D41" s="10" t="inlineStr">
         <is>
           <t>산탄 퍼짐 각도(도).</t>
         </is>
